--- a/Financial Analysis/KOSS.xlsx
+++ b/Financial Analysis/KOSS.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28526"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28827"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\antos\Desktop\Financial Analysis\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\antos\Documents\GitHub\FinanceModels\Financial Analysis\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1EFC766D-0839-41C0-91C4-EF18E8200A96}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8935BF0B-0392-48C6-9B55-5667DB3478CC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" activeTab="1" xr2:uid="{19D304A3-1DD6-4B71-BF92-1FCB4FE2DF3C}"/>
   </bookViews>
@@ -196,7 +196,7 @@
     <t>Consensus</t>
   </si>
   <si>
-    <t>Overvalued</t>
+    <t>Heavily overvalued</t>
   </si>
 </sst>
 </file>
@@ -297,13 +297,13 @@
 <xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
   <xdr:twoCellAnchor>
     <xdr:from>
-      <xdr:col>20</xdr:col>
+      <xdr:col>21</xdr:col>
       <xdr:colOff>15240</xdr:colOff>
       <xdr:row>0</xdr:row>
       <xdr:rowOff>7620</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>20</xdr:col>
+      <xdr:col>21</xdr:col>
       <xdr:colOff>15240</xdr:colOff>
       <xdr:row>33</xdr:row>
       <xdr:rowOff>106680</xdr:rowOff>
@@ -321,7 +321,7 @@
       </xdr:nvCxnSpPr>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="14698980" y="7620"/>
+          <a:off x="15422880" y="7620"/>
           <a:ext cx="0" cy="6134100"/>
         </a:xfrm>
         <a:prstGeom prst="line">
@@ -720,14 +720,14 @@
         <v>1</v>
       </c>
       <c r="D3" s="9">
-        <v>4.33</v>
+        <v>5.79</v>
       </c>
       <c r="E3" s="7">
-        <v>45751</v>
+        <v>45817</v>
       </c>
       <c r="F3" s="7">
         <f ca="1">TODAY()</f>
-        <v>45751</v>
+        <v>45817</v>
       </c>
       <c r="G3" s="7">
         <v>45785</v>
@@ -741,7 +741,7 @@
         <v>9.4</v>
       </c>
       <c r="E4" s="6" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
     </row>
     <row r="5" spans="2:7" x14ac:dyDescent="0.3">
@@ -750,7 +750,7 @@
       </c>
       <c r="D5" s="2">
         <f>D3*D4</f>
-        <v>40.702000000000005</v>
+        <v>54.426000000000002</v>
       </c>
     </row>
     <row r="6" spans="2:7" x14ac:dyDescent="0.3">
@@ -758,11 +758,11 @@
         <v>4</v>
       </c>
       <c r="D6" s="2">
-        <f>2.5+7.2+10</f>
-        <v>19.7</v>
+        <f>2.9+10.1+7</f>
+        <v>20</v>
       </c>
       <c r="E6" s="6" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
     </row>
     <row r="7" spans="2:7" x14ac:dyDescent="0.3">
@@ -773,7 +773,7 @@
         <v>0</v>
       </c>
       <c r="E7" s="6" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
     </row>
     <row r="8" spans="2:7" x14ac:dyDescent="0.3">
@@ -782,7 +782,7 @@
       </c>
       <c r="D8" s="2">
         <f>D6-D7</f>
-        <v>19.7</v>
+        <v>20</v>
       </c>
     </row>
     <row r="9" spans="2:7" x14ac:dyDescent="0.3">
@@ -791,7 +791,7 @@
       </c>
       <c r="D9" s="2">
         <f>D5-D8</f>
-        <v>21.002000000000006</v>
+        <v>34.426000000000002</v>
       </c>
     </row>
   </sheetData>
@@ -1085,12 +1085,11 @@
         <v>3.6</v>
       </c>
       <c r="U3" s="8">
-        <f>Q3*1.05</f>
-        <v>2.7300000000000004</v>
+        <v>2.8</v>
       </c>
       <c r="V3" s="8">
-        <f>R3*1.05</f>
-        <v>3.0449999999999999</v>
+        <f>R3*1.1</f>
+        <v>3.19</v>
       </c>
       <c r="X3" s="8">
         <v>19.5</v>
@@ -1106,47 +1105,47 @@
       </c>
       <c r="AB3" s="8">
         <f>SUM(S3:V3)</f>
-        <v>12.575000000000001</v>
+        <v>12.790000000000001</v>
       </c>
       <c r="AC3" s="8">
-        <f>AB3*1.03</f>
-        <v>12.952250000000001</v>
+        <f>AB3*1.06</f>
+        <v>13.557400000000001</v>
       </c>
       <c r="AD3" s="8">
-        <f>AC3*1.02</f>
-        <v>13.211295000000002</v>
+        <f>AC3*1.04</f>
+        <v>14.099696000000002</v>
       </c>
       <c r="AE3" s="8">
-        <f>AD3*1.02</f>
-        <v>13.475520900000001</v>
+        <f>AD3*1.03</f>
+        <v>14.522686880000002</v>
       </c>
       <c r="AF3" s="8">
         <f>AE3*1.02</f>
-        <v>13.745031318000001</v>
+        <v>14.813140617600002</v>
       </c>
       <c r="AG3" s="8">
         <f t="shared" ref="AG3:AL3" si="0">AF3*1.02</f>
-        <v>14.019931944360001</v>
+        <v>15.109403429952001</v>
       </c>
       <c r="AH3" s="8">
         <f t="shared" si="0"/>
-        <v>14.300330583247202</v>
+        <v>15.411591498551042</v>
       </c>
       <c r="AI3" s="8">
         <f t="shared" si="0"/>
-        <v>14.586337194912147</v>
+        <v>15.719823328522063</v>
       </c>
       <c r="AJ3" s="8">
         <f t="shared" si="0"/>
-        <v>14.87806393881039</v>
+        <v>16.034219795092504</v>
       </c>
       <c r="AK3" s="8">
         <f t="shared" si="0"/>
-        <v>15.175625217586598</v>
+        <v>16.354904190994354</v>
       </c>
       <c r="AL3" s="8">
         <f t="shared" si="0"/>
-        <v>15.479137721938329</v>
+        <v>16.682002274814241</v>
       </c>
     </row>
     <row r="4" spans="2:139" x14ac:dyDescent="0.3">
@@ -1209,12 +1208,11 @@
         <v>2.2000000000000002</v>
       </c>
       <c r="U4" s="2">
-        <f t="shared" ref="U4:V4" si="1">U3-U5</f>
-        <v>1.6653000000000002</v>
+        <v>1.7</v>
       </c>
       <c r="V4" s="2">
-        <f t="shared" si="1"/>
-        <v>1.8574499999999998</v>
+        <f t="shared" ref="U4:V4" si="1">V3-V5</f>
+        <v>1.9459</v>
       </c>
       <c r="X4" s="2">
         <v>12.8</v>
@@ -1230,47 +1228,47 @@
       </c>
       <c r="AB4" s="2">
         <f>SUM(S4:V4)</f>
-        <v>7.7227500000000004</v>
+        <v>7.8459000000000003</v>
       </c>
       <c r="AC4" s="2">
         <f>AC3-AC5</f>
-        <v>7.9008725000000002</v>
+        <v>8.2700139999999998</v>
       </c>
       <c r="AD4" s="2">
         <f t="shared" ref="AD4:AL4" si="2">AD3-AD5</f>
-        <v>8.0588899500000011</v>
+        <v>8.6008145599999999</v>
       </c>
       <c r="AE4" s="2">
         <f t="shared" si="2"/>
-        <v>8.2200677490000018</v>
+        <v>8.8588389968000012</v>
       </c>
       <c r="AF4" s="2">
         <f t="shared" si="2"/>
-        <v>8.384469103979999</v>
+        <v>9.0360157767360008</v>
       </c>
       <c r="AG4" s="2">
         <f t="shared" si="2"/>
-        <v>8.5521584860596001</v>
+        <v>9.2167360922707218</v>
       </c>
       <c r="AH4" s="2">
         <f t="shared" si="2"/>
-        <v>8.7232016557807945</v>
+        <v>9.4010708141161352</v>
       </c>
       <c r="AI4" s="2">
         <f t="shared" si="2"/>
-        <v>8.8976656888964101</v>
+        <v>9.5890922303984585</v>
       </c>
       <c r="AJ4" s="2">
         <f t="shared" si="2"/>
-        <v>9.0756190026743369</v>
+        <v>9.7808740750064267</v>
       </c>
       <c r="AK4" s="2">
         <f t="shared" si="2"/>
-        <v>9.2571313827278239</v>
+        <v>9.9764915565065557</v>
       </c>
       <c r="AL4" s="2">
         <f t="shared" si="2"/>
-        <v>9.4422740103823806</v>
+        <v>10.176021387636688</v>
       </c>
     </row>
     <row r="5" spans="2:139" s="1" customFormat="1" x14ac:dyDescent="0.3">
@@ -1278,7 +1276,7 @@
         <v>21</v>
       </c>
       <c r="C5" s="8">
-        <f t="shared" ref="C5:T5" si="3">C3-C4</f>
+        <f t="shared" ref="C5:U5" si="3">C3-C4</f>
         <v>1.6999999999999988</v>
       </c>
       <c r="D5" s="8">
@@ -1350,12 +1348,12 @@
         <v>1.4</v>
       </c>
       <c r="U5" s="8">
-        <f>U3*0.39</f>
-        <v>1.0647000000000002</v>
+        <f t="shared" si="3"/>
+        <v>1.0999999999999999</v>
       </c>
       <c r="V5" s="8">
         <f>V3*0.39</f>
-        <v>1.1875500000000001</v>
+        <v>1.2441</v>
       </c>
       <c r="X5" s="8">
         <f>X3-X4</f>
@@ -1375,47 +1373,47 @@
       </c>
       <c r="AB5" s="8">
         <f>AB3-AB4</f>
-        <v>4.8522500000000006</v>
+        <v>4.9441000000000006</v>
       </c>
       <c r="AC5" s="8">
         <f>AC3*0.39</f>
-        <v>5.051377500000001</v>
+        <v>5.2873860000000006</v>
       </c>
       <c r="AD5" s="8">
         <f t="shared" ref="AD5:AL5" si="4">AD3*0.39</f>
-        <v>5.1524050500000005</v>
+        <v>5.4988814400000008</v>
       </c>
       <c r="AE5" s="8">
         <f t="shared" si="4"/>
-        <v>5.2554531510000002</v>
+        <v>5.6638478832000008</v>
       </c>
       <c r="AF5" s="8">
         <f t="shared" si="4"/>
-        <v>5.3605622140200007</v>
+        <v>5.7771248408640012</v>
       </c>
       <c r="AG5" s="8">
         <f t="shared" si="4"/>
-        <v>5.4677734583004005</v>
+        <v>5.8926673376812806</v>
       </c>
       <c r="AH5" s="8">
         <f t="shared" si="4"/>
-        <v>5.5771289274664086</v>
+        <v>6.0105206844349066</v>
       </c>
       <c r="AI5" s="8">
         <f t="shared" si="4"/>
-        <v>5.688671506015738</v>
+        <v>6.1307310981236043</v>
       </c>
       <c r="AJ5" s="8">
         <f t="shared" si="4"/>
-        <v>5.8024449361360526</v>
+        <v>6.2533457200860765</v>
       </c>
       <c r="AK5" s="8">
         <f t="shared" si="4"/>
-        <v>5.918493834858773</v>
+        <v>6.3784126344877983</v>
       </c>
       <c r="AL5" s="8">
         <f t="shared" si="4"/>
-        <v>6.0368637115559487</v>
+        <v>6.5059808871775546</v>
       </c>
     </row>
     <row r="6" spans="2:139" x14ac:dyDescent="0.3">
@@ -1478,12 +1476,11 @@
         <v>1.5</v>
       </c>
       <c r="U6" s="2">
-        <f t="shared" ref="U6" si="5">Q6*1.01</f>
-        <v>1.5150000000000001</v>
+        <v>1.6</v>
       </c>
       <c r="V6" s="2">
-        <f>R6*0.98</f>
-        <v>1.47</v>
+        <f>R6*1.04</f>
+        <v>1.56</v>
       </c>
       <c r="X6" s="2">
         <v>7.1</v>
@@ -1499,47 +1496,47 @@
       </c>
       <c r="AB6" s="2">
         <f>SUM(S6:V6)</f>
-        <v>6.2849999999999993</v>
+        <v>6.4600000000000009</v>
       </c>
       <c r="AC6" s="2">
         <f>AB6*0.99</f>
-        <v>6.2221499999999992</v>
+        <v>6.3954000000000004</v>
       </c>
       <c r="AD6" s="2">
-        <f t="shared" ref="AD6:AL6" si="6">AC6*0.99</f>
-        <v>6.1599284999999995</v>
+        <f t="shared" ref="AD6:AL6" si="5">AC6*0.99</f>
+        <v>6.3314460000000006</v>
       </c>
       <c r="AE6" s="2">
-        <f t="shared" si="6"/>
-        <v>6.0983292149999997</v>
+        <f t="shared" si="5"/>
+        <v>6.2681315400000006</v>
       </c>
       <c r="AF6" s="2">
-        <f t="shared" si="6"/>
-        <v>6.0373459228499993</v>
+        <f t="shared" si="5"/>
+        <v>6.2054502246000007</v>
       </c>
       <c r="AG6" s="2">
-        <f t="shared" si="6"/>
-        <v>5.9769724636214994</v>
+        <f t="shared" si="5"/>
+        <v>6.1433957223540006</v>
       </c>
       <c r="AH6" s="2">
-        <f t="shared" si="6"/>
-        <v>5.9172027389852841</v>
+        <f t="shared" si="5"/>
+        <v>6.0819617651304601</v>
       </c>
       <c r="AI6" s="2">
-        <f t="shared" si="6"/>
-        <v>5.8580307115954309</v>
+        <f t="shared" si="5"/>
+        <v>6.0211421474791553</v>
       </c>
       <c r="AJ6" s="2">
-        <f t="shared" si="6"/>
-        <v>5.7994504044794768</v>
+        <f t="shared" si="5"/>
+        <v>5.9609307260043636</v>
       </c>
       <c r="AK6" s="2">
-        <f t="shared" si="6"/>
-        <v>5.7414559004346817</v>
+        <f t="shared" si="5"/>
+        <v>5.9013214187443195</v>
       </c>
       <c r="AL6" s="2">
-        <f t="shared" si="6"/>
-        <v>5.6840413414303352</v>
+        <f t="shared" si="5"/>
+        <v>5.8423082045568764</v>
       </c>
     </row>
     <row r="7" spans="2:139" s="1" customFormat="1" x14ac:dyDescent="0.3">
@@ -1547,84 +1544,84 @@
         <v>23</v>
       </c>
       <c r="C7" s="8">
-        <f t="shared" ref="C7:S7" si="7">C5-C6</f>
+        <f t="shared" ref="C7:S7" si="6">C5-C6</f>
         <v>0.19999999999999862</v>
       </c>
       <c r="D7" s="8">
+        <f t="shared" si="6"/>
+        <v>0</v>
+      </c>
+      <c r="E7" s="8">
+        <f t="shared" si="6"/>
+        <v>-0.89999999999999991</v>
+      </c>
+      <c r="F7" s="8">
+        <f t="shared" si="6"/>
+        <v>0.30000000000000049</v>
+      </c>
+      <c r="G7" s="8">
+        <f t="shared" si="6"/>
+        <v>-0.19999999999999951</v>
+      </c>
+      <c r="H7" s="8">
+        <f t="shared" si="6"/>
+        <v>0.30000000000000049</v>
+      </c>
+      <c r="I7" s="8">
+        <f t="shared" si="6"/>
+        <v>0.29999999999999938</v>
+      </c>
+      <c r="J7" s="8">
+        <f t="shared" si="6"/>
+        <v>0.39999999999999991</v>
+      </c>
+      <c r="K7" s="8">
+        <f t="shared" si="6"/>
+        <v>-22.5</v>
+      </c>
+      <c r="L7" s="8">
+        <f t="shared" si="6"/>
+        <v>-1.3000000000000003</v>
+      </c>
+      <c r="M7" s="8">
+        <f t="shared" si="6"/>
+        <v>-0.40000000000000013</v>
+      </c>
+      <c r="N7" s="8">
+        <f t="shared" si="6"/>
+        <v>-0.59999999999999964</v>
+      </c>
+      <c r="O7" s="8">
+        <f t="shared" si="6"/>
+        <v>-0.39999999999999991</v>
+      </c>
+      <c r="P7" s="8">
+        <f t="shared" si="6"/>
+        <v>-0.5</v>
+      </c>
+      <c r="Q7" s="8">
+        <f t="shared" si="6"/>
+        <v>-0.7</v>
+      </c>
+      <c r="R7" s="8">
+        <f t="shared" si="6"/>
+        <v>-0.30000000000000004</v>
+      </c>
+      <c r="S7" s="8">
+        <f t="shared" si="6"/>
+        <v>-0.59999999999999987</v>
+      </c>
+      <c r="T7" s="8">
+        <f t="shared" ref="T7:V7" si="7">T5-T6</f>
+        <v>-0.10000000000000009</v>
+      </c>
+      <c r="U7" s="8">
         <f t="shared" si="7"/>
-        <v>0</v>
-      </c>
-      <c r="E7" s="8">
+        <v>-0.50000000000000022</v>
+      </c>
+      <c r="V7" s="8">
         <f t="shared" si="7"/>
-        <v>-0.89999999999999991</v>
-      </c>
-      <c r="F7" s="8">
-        <f t="shared" si="7"/>
-        <v>0.30000000000000049</v>
-      </c>
-      <c r="G7" s="8">
-        <f t="shared" si="7"/>
-        <v>-0.19999999999999951</v>
-      </c>
-      <c r="H7" s="8">
-        <f t="shared" si="7"/>
-        <v>0.30000000000000049</v>
-      </c>
-      <c r="I7" s="8">
-        <f t="shared" si="7"/>
-        <v>0.29999999999999938</v>
-      </c>
-      <c r="J7" s="8">
-        <f t="shared" si="7"/>
-        <v>0.39999999999999991</v>
-      </c>
-      <c r="K7" s="8">
-        <f t="shared" si="7"/>
-        <v>-22.5</v>
-      </c>
-      <c r="L7" s="8">
-        <f t="shared" si="7"/>
-        <v>-1.3000000000000003</v>
-      </c>
-      <c r="M7" s="8">
-        <f t="shared" si="7"/>
-        <v>-0.40000000000000013</v>
-      </c>
-      <c r="N7" s="8">
-        <f t="shared" si="7"/>
-        <v>-0.59999999999999964</v>
-      </c>
-      <c r="O7" s="8">
-        <f t="shared" si="7"/>
-        <v>-0.39999999999999991</v>
-      </c>
-      <c r="P7" s="8">
-        <f t="shared" si="7"/>
-        <v>-0.5</v>
-      </c>
-      <c r="Q7" s="8">
-        <f t="shared" si="7"/>
-        <v>-0.7</v>
-      </c>
-      <c r="R7" s="8">
-        <f t="shared" si="7"/>
-        <v>-0.30000000000000004</v>
-      </c>
-      <c r="S7" s="8">
-        <f t="shared" si="7"/>
-        <v>-0.59999999999999987</v>
-      </c>
-      <c r="T7" s="8">
-        <f t="shared" ref="T7:V7" si="8">T5-T6</f>
-        <v>-0.10000000000000009</v>
-      </c>
-      <c r="U7" s="8">
-        <f t="shared" si="8"/>
-        <v>-0.45029999999999992</v>
-      </c>
-      <c r="V7" s="8">
-        <f t="shared" si="8"/>
-        <v>-0.28244999999999987</v>
+        <v>-0.31590000000000007</v>
       </c>
       <c r="X7" s="8">
         <f>X5-X6</f>
@@ -1644,47 +1641,47 @@
       </c>
       <c r="AB7" s="8">
         <f>AB5-AB6</f>
-        <v>-1.4327499999999986</v>
+        <v>-1.5159000000000002</v>
       </c>
       <c r="AC7" s="8">
-        <f t="shared" ref="AC7:AL7" si="9">AC5-AC6</f>
-        <v>-1.1707724999999982</v>
+        <f t="shared" ref="AC7:AL7" si="8">AC5-AC6</f>
+        <v>-1.1080139999999998</v>
       </c>
       <c r="AD7" s="8">
-        <f t="shared" si="9"/>
-        <v>-1.007523449999999</v>
+        <f t="shared" si="8"/>
+        <v>-0.83256455999999979</v>
       </c>
       <c r="AE7" s="8">
-        <f t="shared" si="9"/>
-        <v>-0.84287606399999948</v>
+        <f t="shared" si="8"/>
+        <v>-0.60428365679999985</v>
       </c>
       <c r="AF7" s="8">
-        <f t="shared" si="9"/>
-        <v>-0.67678370882999861</v>
+        <f t="shared" si="8"/>
+        <v>-0.42832538373599949</v>
       </c>
       <c r="AG7" s="8">
-        <f t="shared" si="9"/>
-        <v>-0.50919900532109885</v>
+        <f t="shared" si="8"/>
+        <v>-0.25072838467271996</v>
       </c>
       <c r="AH7" s="8">
-        <f t="shared" si="9"/>
-        <v>-0.3400738115188755</v>
+        <f t="shared" si="8"/>
+        <v>-7.1441080695553438E-2</v>
       </c>
       <c r="AI7" s="8">
-        <f t="shared" si="9"/>
-        <v>-0.16935920557969286</v>
+        <f t="shared" si="8"/>
+        <v>0.10958895064444896</v>
       </c>
       <c r="AJ7" s="8">
-        <f t="shared" si="9"/>
-        <v>2.9945316565758162E-3</v>
+        <f t="shared" si="8"/>
+        <v>0.2924149940817129</v>
       </c>
       <c r="AK7" s="8">
-        <f t="shared" si="9"/>
-        <v>0.17703793442409133</v>
+        <f t="shared" si="8"/>
+        <v>0.47709121574347879</v>
       </c>
       <c r="AL7" s="8">
-        <f t="shared" si="9"/>
-        <v>0.35282237012561346</v>
+        <f t="shared" si="8"/>
+        <v>0.66367268262067824</v>
       </c>
     </row>
     <row r="8" spans="2:139" x14ac:dyDescent="0.3">
@@ -1885,39 +1882,39 @@
         <v>-0.81600000000000006</v>
       </c>
       <c r="AD9" s="2">
-        <f t="shared" ref="AD9:AL9" si="10">AC9*1.02</f>
+        <f t="shared" ref="AD9:AL9" si="9">AC9*1.02</f>
         <v>-0.83232000000000006</v>
       </c>
       <c r="AE9" s="2">
-        <f t="shared" si="10"/>
+        <f t="shared" si="9"/>
         <v>-0.84896640000000012</v>
       </c>
       <c r="AF9" s="2">
-        <f t="shared" si="10"/>
+        <f t="shared" si="9"/>
         <v>-0.86594572800000014</v>
       </c>
       <c r="AG9" s="2">
-        <f t="shared" si="10"/>
+        <f t="shared" si="9"/>
         <v>-0.88326464256000015</v>
       </c>
       <c r="AH9" s="2">
-        <f t="shared" si="10"/>
+        <f t="shared" si="9"/>
         <v>-0.90092993541120014</v>
       </c>
       <c r="AI9" s="2">
-        <f t="shared" si="10"/>
+        <f t="shared" si="9"/>
         <v>-0.91894853411942412</v>
       </c>
       <c r="AJ9" s="2">
-        <f t="shared" si="10"/>
+        <f t="shared" si="9"/>
         <v>-0.93732750480181259</v>
       </c>
       <c r="AK9" s="2">
-        <f t="shared" si="10"/>
+        <f t="shared" si="9"/>
         <v>-0.95607405489784891</v>
       </c>
       <c r="AL9" s="2">
-        <f t="shared" si="10"/>
+        <f t="shared" si="9"/>
         <v>-0.97519553599580588</v>
       </c>
     </row>
@@ -1926,84 +1923,84 @@
         <v>26</v>
       </c>
       <c r="C10" s="8">
-        <f t="shared" ref="C10:S10" si="11">C7-C8-C9</f>
+        <f t="shared" ref="C10:S10" si="10">C7-C8-C9</f>
         <v>0.19999999999999862</v>
       </c>
       <c r="D10" s="8">
+        <f t="shared" si="10"/>
+        <v>0.5</v>
+      </c>
+      <c r="E10" s="8">
+        <f t="shared" si="10"/>
+        <v>-0.49999999999999989</v>
+      </c>
+      <c r="F10" s="8">
+        <f t="shared" si="10"/>
+        <v>0.30000000000000049</v>
+      </c>
+      <c r="G10" s="8">
+        <f t="shared" si="10"/>
+        <v>-9.9999999999999506E-2</v>
+      </c>
+      <c r="H10" s="8">
+        <f t="shared" si="10"/>
+        <v>0.60000000000000053</v>
+      </c>
+      <c r="I10" s="8">
+        <f t="shared" si="10"/>
+        <v>0.29999999999999938</v>
+      </c>
+      <c r="J10" s="8">
+        <f t="shared" si="10"/>
+        <v>0.39999999999999991</v>
+      </c>
+      <c r="K10" s="8">
+        <f t="shared" si="10"/>
+        <v>10.5</v>
+      </c>
+      <c r="L10" s="8">
+        <f t="shared" si="10"/>
+        <v>-1.2000000000000002</v>
+      </c>
+      <c r="M10" s="8">
+        <f t="shared" si="10"/>
+        <v>-0.20000000000000012</v>
+      </c>
+      <c r="N10" s="8">
+        <f t="shared" si="10"/>
+        <v>-0.39999999999999963</v>
+      </c>
+      <c r="O10" s="8">
+        <f t="shared" si="10"/>
+        <v>-0.1999999999999999</v>
+      </c>
+      <c r="P10" s="8">
+        <f t="shared" si="10"/>
+        <v>-0.3</v>
+      </c>
+      <c r="Q10" s="8">
+        <f t="shared" si="10"/>
+        <v>-0.49999999999999994</v>
+      </c>
+      <c r="R10" s="8">
+        <f t="shared" si="10"/>
+        <v>-0.10000000000000003</v>
+      </c>
+      <c r="S10" s="8">
+        <f t="shared" si="10"/>
+        <v>-0.39999999999999986</v>
+      </c>
+      <c r="T10" s="8">
+        <f t="shared" ref="T10:V10" si="11">T7-T8-T9</f>
+        <v>9.9999999999999922E-2</v>
+      </c>
+      <c r="U10" s="8">
         <f t="shared" si="11"/>
-        <v>0.5</v>
-      </c>
-      <c r="E10" s="8">
+        <v>-0.30000000000000021</v>
+      </c>
+      <c r="V10" s="8">
         <f t="shared" si="11"/>
-        <v>-0.49999999999999989</v>
-      </c>
-      <c r="F10" s="8">
-        <f t="shared" si="11"/>
-        <v>0.30000000000000049</v>
-      </c>
-      <c r="G10" s="8">
-        <f t="shared" si="11"/>
-        <v>-9.9999999999999506E-2</v>
-      </c>
-      <c r="H10" s="8">
-        <f t="shared" si="11"/>
-        <v>0.60000000000000053</v>
-      </c>
-      <c r="I10" s="8">
-        <f t="shared" si="11"/>
-        <v>0.29999999999999938</v>
-      </c>
-      <c r="J10" s="8">
-        <f t="shared" si="11"/>
-        <v>0.39999999999999991</v>
-      </c>
-      <c r="K10" s="8">
-        <f t="shared" si="11"/>
-        <v>10.5</v>
-      </c>
-      <c r="L10" s="8">
-        <f t="shared" si="11"/>
-        <v>-1.2000000000000002</v>
-      </c>
-      <c r="M10" s="8">
-        <f t="shared" si="11"/>
-        <v>-0.20000000000000012</v>
-      </c>
-      <c r="N10" s="8">
-        <f t="shared" si="11"/>
-        <v>-0.39999999999999963</v>
-      </c>
-      <c r="O10" s="8">
-        <f t="shared" si="11"/>
-        <v>-0.1999999999999999</v>
-      </c>
-      <c r="P10" s="8">
-        <f t="shared" si="11"/>
-        <v>-0.3</v>
-      </c>
-      <c r="Q10" s="8">
-        <f t="shared" si="11"/>
-        <v>-0.49999999999999994</v>
-      </c>
-      <c r="R10" s="8">
-        <f t="shared" si="11"/>
-        <v>-0.10000000000000003</v>
-      </c>
-      <c r="S10" s="8">
-        <f t="shared" si="11"/>
-        <v>-0.39999999999999986</v>
-      </c>
-      <c r="T10" s="8">
-        <f t="shared" ref="T10:V10" si="12">T7-T8-T9</f>
-        <v>9.9999999999999922E-2</v>
-      </c>
-      <c r="U10" s="8">
-        <f t="shared" si="12"/>
-        <v>-0.25029999999999991</v>
-      </c>
-      <c r="V10" s="8">
-        <f t="shared" si="12"/>
-        <v>-8.2449999999999857E-2</v>
+        <v>-0.11590000000000006</v>
       </c>
       <c r="X10" s="8">
         <f>X7-X8-X9</f>
@@ -2023,47 +2020,47 @@
       </c>
       <c r="AB10" s="8">
         <f>AB7-AB8-AB9</f>
-        <v>-0.63274999999999859</v>
+        <v>-0.7159000000000002</v>
       </c>
       <c r="AC10" s="8">
-        <f t="shared" ref="AC10:AL10" si="13">AC7-AC8-AC9</f>
-        <v>-0.35477249999999816</v>
+        <f t="shared" ref="AC10:AL10" si="12">AC7-AC8-AC9</f>
+        <v>-0.29201399999999977</v>
       </c>
       <c r="AD10" s="8">
-        <f t="shared" si="13"/>
-        <v>-0.17520344999999893</v>
+        <f t="shared" si="12"/>
+        <v>-2.4455999999972722E-4</v>
       </c>
       <c r="AE10" s="8">
-        <f t="shared" si="13"/>
-        <v>6.0903360000006401E-3</v>
+        <f t="shared" si="12"/>
+        <v>0.24468274320000027</v>
       </c>
       <c r="AF10" s="8">
-        <f t="shared" si="13"/>
-        <v>0.18916201917000153</v>
+        <f t="shared" si="12"/>
+        <v>0.43762034426400065</v>
       </c>
       <c r="AG10" s="8">
-        <f t="shared" si="13"/>
-        <v>0.37406563723890129</v>
+        <f t="shared" si="12"/>
+        <v>0.63253625788728018</v>
       </c>
       <c r="AH10" s="8">
-        <f t="shared" si="13"/>
-        <v>0.56085612389232464</v>
+        <f t="shared" si="12"/>
+        <v>0.82948885471564671</v>
       </c>
       <c r="AI10" s="8">
-        <f t="shared" si="13"/>
-        <v>0.74958932853973126</v>
+        <f t="shared" si="12"/>
+        <v>1.0285374847638731</v>
       </c>
       <c r="AJ10" s="8">
-        <f t="shared" si="13"/>
-        <v>0.94032203645838841</v>
+        <f t="shared" si="12"/>
+        <v>1.2297424988835255</v>
       </c>
       <c r="AK10" s="8">
-        <f t="shared" si="13"/>
-        <v>1.1331119893219403</v>
+        <f t="shared" si="12"/>
+        <v>1.4331652706413278</v>
       </c>
       <c r="AL10" s="8">
-        <f t="shared" si="13"/>
-        <v>1.3280179061214192</v>
+        <f t="shared" si="12"/>
+        <v>1.638868218616484</v>
       </c>
     </row>
     <row r="11" spans="2:139" x14ac:dyDescent="0.3">
@@ -2183,548 +2180,548 @@
         <v>28</v>
       </c>
       <c r="C12" s="8">
-        <f t="shared" ref="C12:S12" si="14">C10-C11</f>
+        <f t="shared" ref="C12:S12" si="13">C10-C11</f>
         <v>0.19999999999999862</v>
       </c>
       <c r="D12" s="8">
+        <f t="shared" si="13"/>
+        <v>0.5</v>
+      </c>
+      <c r="E12" s="8">
+        <f t="shared" si="13"/>
+        <v>-0.49999999999999989</v>
+      </c>
+      <c r="F12" s="8">
+        <f t="shared" si="13"/>
+        <v>0.30000000000000049</v>
+      </c>
+      <c r="G12" s="8">
+        <f t="shared" si="13"/>
+        <v>-9.9999999999999506E-2</v>
+      </c>
+      <c r="H12" s="8">
+        <f t="shared" si="13"/>
+        <v>0.60000000000000053</v>
+      </c>
+      <c r="I12" s="8">
+        <f t="shared" si="13"/>
+        <v>0.29999999999999938</v>
+      </c>
+      <c r="J12" s="8">
+        <f t="shared" si="13"/>
+        <v>0.39999999999999991</v>
+      </c>
+      <c r="K12" s="8">
+        <f t="shared" si="13"/>
+        <v>9.9</v>
+      </c>
+      <c r="L12" s="8">
+        <f t="shared" si="13"/>
+        <v>-1.1000000000000001</v>
+      </c>
+      <c r="M12" s="8">
+        <f t="shared" si="13"/>
+        <v>-0.20000000000000012</v>
+      </c>
+      <c r="N12" s="8">
+        <f t="shared" si="13"/>
+        <v>-0.2999999999999996</v>
+      </c>
+      <c r="O12" s="8">
+        <f t="shared" si="13"/>
+        <v>-0.1999999999999999</v>
+      </c>
+      <c r="P12" s="8">
+        <f t="shared" si="13"/>
+        <v>-0.3</v>
+      </c>
+      <c r="Q12" s="8">
+        <f t="shared" si="13"/>
+        <v>-0.39999999999999991</v>
+      </c>
+      <c r="R12" s="8">
+        <f t="shared" si="13"/>
+        <v>-0.10000000000000003</v>
+      </c>
+      <c r="S12" s="8">
+        <f t="shared" si="13"/>
+        <v>-0.39999999999999986</v>
+      </c>
+      <c r="T12" s="8">
+        <f t="shared" ref="T12:V12" si="14">T10-T11</f>
+        <v>9.9999999999999922E-2</v>
+      </c>
+      <c r="U12" s="8">
         <f t="shared" si="14"/>
-        <v>0.5</v>
-      </c>
-      <c r="E12" s="8">
+        <v>-0.30000000000000021</v>
+      </c>
+      <c r="V12" s="8">
         <f t="shared" si="14"/>
-        <v>-0.49999999999999989</v>
-      </c>
-      <c r="F12" s="8">
-        <f t="shared" si="14"/>
-        <v>0.30000000000000049</v>
-      </c>
-      <c r="G12" s="8">
-        <f t="shared" si="14"/>
-        <v>-9.9999999999999506E-2</v>
-      </c>
-      <c r="H12" s="8">
-        <f t="shared" si="14"/>
-        <v>0.60000000000000053</v>
-      </c>
-      <c r="I12" s="8">
-        <f t="shared" si="14"/>
-        <v>0.29999999999999938</v>
-      </c>
-      <c r="J12" s="8">
-        <f t="shared" si="14"/>
-        <v>0.39999999999999991</v>
-      </c>
-      <c r="K12" s="8">
-        <f t="shared" si="14"/>
-        <v>9.9</v>
-      </c>
-      <c r="L12" s="8">
-        <f t="shared" si="14"/>
-        <v>-1.1000000000000001</v>
-      </c>
-      <c r="M12" s="8">
-        <f t="shared" si="14"/>
-        <v>-0.20000000000000012</v>
-      </c>
-      <c r="N12" s="8">
-        <f t="shared" si="14"/>
-        <v>-0.2999999999999996</v>
-      </c>
-      <c r="O12" s="8">
-        <f t="shared" si="14"/>
-        <v>-0.1999999999999999</v>
-      </c>
-      <c r="P12" s="8">
-        <f t="shared" si="14"/>
-        <v>-0.3</v>
-      </c>
-      <c r="Q12" s="8">
-        <f t="shared" si="14"/>
-        <v>-0.39999999999999991</v>
-      </c>
-      <c r="R12" s="8">
-        <f t="shared" si="14"/>
-        <v>-0.10000000000000003</v>
-      </c>
-      <c r="S12" s="8">
-        <f t="shared" si="14"/>
-        <v>-0.39999999999999986</v>
-      </c>
-      <c r="T12" s="8">
-        <f t="shared" ref="T12:V12" si="15">T10-T11</f>
-        <v>9.9999999999999922E-2</v>
-      </c>
-      <c r="U12" s="8">
+        <v>-0.11590000000000006</v>
+      </c>
+      <c r="X12" s="8">
+        <f t="shared" ref="X12:AC12" si="15">X10-X11</f>
+        <v>0.49999999999999967</v>
+      </c>
+      <c r="Y12" s="8">
         <f t="shared" si="15"/>
-        <v>-0.25029999999999991</v>
-      </c>
-      <c r="V12" s="8">
+        <v>1.3000000000000012</v>
+      </c>
+      <c r="Z12" s="8">
         <f t="shared" si="15"/>
-        <v>-8.2449999999999857E-2</v>
-      </c>
-      <c r="X12" s="8">
-        <f t="shared" ref="X12:AC12" si="16">X10-X11</f>
-        <v>0.49999999999999967</v>
-      </c>
-      <c r="Y12" s="8">
+        <v>8.3999999999999986</v>
+      </c>
+      <c r="AA12" s="8">
+        <f t="shared" si="15"/>
+        <v>-0.99999999999999856</v>
+      </c>
+      <c r="AB12" s="8">
+        <f t="shared" si="15"/>
+        <v>-0.7159000000000002</v>
+      </c>
+      <c r="AC12" s="8">
+        <f t="shared" si="15"/>
+        <v>-0.29201399999999977</v>
+      </c>
+      <c r="AD12" s="8">
+        <f t="shared" ref="AD12:AL12" si="16">AD10-AD11</f>
+        <v>-2.4455999999972722E-4</v>
+      </c>
+      <c r="AE12" s="8">
         <f t="shared" si="16"/>
-        <v>1.3000000000000012</v>
-      </c>
-      <c r="Z12" s="8">
+        <v>0.24468274320000027</v>
+      </c>
+      <c r="AF12" s="8">
         <f t="shared" si="16"/>
-        <v>8.3999999999999986</v>
-      </c>
-      <c r="AA12" s="8">
+        <v>0.43762034426400065</v>
+      </c>
+      <c r="AG12" s="8">
         <f t="shared" si="16"/>
-        <v>-0.99999999999999856</v>
-      </c>
-      <c r="AB12" s="8">
+        <v>0.63253625788728018</v>
+      </c>
+      <c r="AH12" s="8">
         <f t="shared" si="16"/>
-        <v>-0.63274999999999859</v>
-      </c>
-      <c r="AC12" s="8">
+        <v>0.82948885471564671</v>
+      </c>
+      <c r="AI12" s="8">
         <f t="shared" si="16"/>
-        <v>-0.35477249999999816</v>
-      </c>
-      <c r="AD12" s="8">
-        <f t="shared" ref="AD12:AL12" si="17">AD10-AD11</f>
-        <v>-0.17520344999999893</v>
-      </c>
-      <c r="AE12" s="8">
-        <f t="shared" si="17"/>
-        <v>6.0903360000006401E-3</v>
-      </c>
-      <c r="AF12" s="8">
-        <f t="shared" si="17"/>
-        <v>0.18916201917000153</v>
-      </c>
-      <c r="AG12" s="8">
-        <f t="shared" si="17"/>
-        <v>0.37406563723890129</v>
-      </c>
-      <c r="AH12" s="8">
-        <f t="shared" si="17"/>
-        <v>0.56085612389232464</v>
-      </c>
-      <c r="AI12" s="8">
-        <f t="shared" si="17"/>
-        <v>0.74958932853973126</v>
+        <v>1.0285374847638731</v>
       </c>
       <c r="AJ12" s="8">
-        <f t="shared" si="17"/>
-        <v>0.94032203645838841</v>
+        <f t="shared" si="16"/>
+        <v>1.2297424988835255</v>
       </c>
       <c r="AK12" s="8">
-        <f t="shared" si="17"/>
-        <v>1.1331119893219403</v>
+        <f t="shared" si="16"/>
+        <v>1.4331652706413278</v>
       </c>
       <c r="AL12" s="8">
-        <f t="shared" si="17"/>
-        <v>1.3280179061214192</v>
+        <f t="shared" si="16"/>
+        <v>1.638868218616484</v>
       </c>
       <c r="AM12" s="1">
         <f>AL12*(1+$AO$17)</f>
-        <v>1.314737727060205</v>
+        <v>1.6224795364303191</v>
       </c>
       <c r="AN12" s="1">
-        <f t="shared" ref="AN12:CY12" si="18">AM12*(1+$AO$17)</f>
-        <v>1.3015903497896029</v>
+        <f t="shared" ref="AN12:CY12" si="17">AM12*(1+$AO$17)</f>
+        <v>1.606254741066016</v>
       </c>
       <c r="AO12" s="1">
+        <f t="shared" si="17"/>
+        <v>1.5901921936553558</v>
+      </c>
+      <c r="AP12" s="1">
+        <f t="shared" si="17"/>
+        <v>1.5742902717188023</v>
+      </c>
+      <c r="AQ12" s="1">
+        <f t="shared" si="17"/>
+        <v>1.5585473690016143</v>
+      </c>
+      <c r="AR12" s="1">
+        <f t="shared" si="17"/>
+        <v>1.5429618953115982</v>
+      </c>
+      <c r="AS12" s="1">
+        <f t="shared" si="17"/>
+        <v>1.5275322763584822</v>
+      </c>
+      <c r="AT12" s="1">
+        <f t="shared" si="17"/>
+        <v>1.5122569535948973</v>
+      </c>
+      <c r="AU12" s="1">
+        <f t="shared" si="17"/>
+        <v>1.4971343840589484</v>
+      </c>
+      <c r="AV12" s="1">
+        <f t="shared" si="17"/>
+        <v>1.482163040218359</v>
+      </c>
+      <c r="AW12" s="1">
+        <f t="shared" si="17"/>
+        <v>1.4673414098161754</v>
+      </c>
+      <c r="AX12" s="1">
+        <f t="shared" si="17"/>
+        <v>1.4526679957180137</v>
+      </c>
+      <c r="AY12" s="1">
+        <f t="shared" si="17"/>
+        <v>1.4381413157608336</v>
+      </c>
+      <c r="AZ12" s="1">
+        <f t="shared" si="17"/>
+        <v>1.4237599026032253</v>
+      </c>
+      <c r="BA12" s="1">
+        <f t="shared" si="17"/>
+        <v>1.4095223035771931</v>
+      </c>
+      <c r="BB12" s="1">
+        <f t="shared" si="17"/>
+        <v>1.3954270805414211</v>
+      </c>
+      <c r="BC12" s="1">
+        <f t="shared" si="17"/>
+        <v>1.3814728097360069</v>
+      </c>
+      <c r="BD12" s="1">
+        <f t="shared" si="17"/>
+        <v>1.3676580816386468</v>
+      </c>
+      <c r="BE12" s="1">
+        <f t="shared" si="17"/>
+        <v>1.3539815008222602</v>
+      </c>
+      <c r="BF12" s="1">
+        <f t="shared" si="17"/>
+        <v>1.3404416858140376</v>
+      </c>
+      <c r="BG12" s="1">
+        <f t="shared" si="17"/>
+        <v>1.3270372689558971</v>
+      </c>
+      <c r="BH12" s="1">
+        <f t="shared" si="17"/>
+        <v>1.3137668962663382</v>
+      </c>
+      <c r="BI12" s="1">
+        <f t="shared" si="17"/>
+        <v>1.3006292273036748</v>
+      </c>
+      <c r="BJ12" s="1">
+        <f t="shared" si="17"/>
+        <v>1.2876229350306381</v>
+      </c>
+      <c r="BK12" s="1">
+        <f t="shared" si="17"/>
+        <v>1.2747467056803317</v>
+      </c>
+      <c r="BL12" s="1">
+        <f t="shared" si="17"/>
+        <v>1.2619992386235284</v>
+      </c>
+      <c r="BM12" s="1">
+        <f t="shared" si="17"/>
+        <v>1.249379246237293</v>
+      </c>
+      <c r="BN12" s="1">
+        <f t="shared" si="17"/>
+        <v>1.2368854537749201</v>
+      </c>
+      <c r="BO12" s="1">
+        <f t="shared" si="17"/>
+        <v>1.2245165992371709</v>
+      </c>
+      <c r="BP12" s="1">
+        <f t="shared" si="17"/>
+        <v>1.2122714332447992</v>
+      </c>
+      <c r="BQ12" s="1">
+        <f t="shared" si="17"/>
+        <v>1.2001487189123512</v>
+      </c>
+      <c r="BR12" s="1">
+        <f t="shared" si="17"/>
+        <v>1.1881472317232278</v>
+      </c>
+      <c r="BS12" s="1">
+        <f t="shared" si="17"/>
+        <v>1.1762657594059955</v>
+      </c>
+      <c r="BT12" s="1">
+        <f t="shared" si="17"/>
+        <v>1.1645031018119356</v>
+      </c>
+      <c r="BU12" s="1">
+        <f t="shared" si="17"/>
+        <v>1.1528580707938163</v>
+      </c>
+      <c r="BV12" s="1">
+        <f t="shared" si="17"/>
+        <v>1.1413294900858781</v>
+      </c>
+      <c r="BW12" s="1">
+        <f t="shared" si="17"/>
+        <v>1.1299161951850194</v>
+      </c>
+      <c r="BX12" s="1">
+        <f t="shared" si="17"/>
+        <v>1.1186170332331693</v>
+      </c>
+      <c r="BY12" s="1">
+        <f t="shared" si="17"/>
+        <v>1.1074308629008376</v>
+      </c>
+      <c r="BZ12" s="1">
+        <f t="shared" si="17"/>
+        <v>1.0963565542718292</v>
+      </c>
+      <c r="CA12" s="1">
+        <f t="shared" si="17"/>
+        <v>1.0853929887291109</v>
+      </c>
+      <c r="CB12" s="1">
+        <f t="shared" si="17"/>
+        <v>1.0745390588418198</v>
+      </c>
+      <c r="CC12" s="1">
+        <f t="shared" si="17"/>
+        <v>1.0637936682534015</v>
+      </c>
+      <c r="CD12" s="1">
+        <f t="shared" si="17"/>
+        <v>1.0531557315708675</v>
+      </c>
+      <c r="CE12" s="1">
+        <f t="shared" si="17"/>
+        <v>1.0426241742551587</v>
+      </c>
+      <c r="CF12" s="1">
+        <f t="shared" si="17"/>
+        <v>1.0321979325126072</v>
+      </c>
+      <c r="CG12" s="1">
+        <f t="shared" si="17"/>
+        <v>1.021875953187481</v>
+      </c>
+      <c r="CH12" s="1">
+        <f t="shared" si="17"/>
+        <v>1.0116571936556062</v>
+      </c>
+      <c r="CI12" s="1">
+        <f t="shared" si="17"/>
+        <v>1.0015406217190501</v>
+      </c>
+      <c r="CJ12" s="1">
+        <f t="shared" si="17"/>
+        <v>0.99152521550185957</v>
+      </c>
+      <c r="CK12" s="1">
+        <f t="shared" si="17"/>
+        <v>0.98160996334684092</v>
+      </c>
+      <c r="CL12" s="1">
+        <f t="shared" si="17"/>
+        <v>0.97179386371337251</v>
+      </c>
+      <c r="CM12" s="1">
+        <f t="shared" si="17"/>
+        <v>0.96207592507623874</v>
+      </c>
+      <c r="CN12" s="1">
+        <f t="shared" si="17"/>
+        <v>0.95245516582547629</v>
+      </c>
+      <c r="CO12" s="1">
+        <f t="shared" si="17"/>
+        <v>0.94293061416722157</v>
+      </c>
+      <c r="CP12" s="1">
+        <f t="shared" si="17"/>
+        <v>0.93350130802554931</v>
+      </c>
+      <c r="CQ12" s="1">
+        <f t="shared" si="17"/>
+        <v>0.92416629494529379</v>
+      </c>
+      <c r="CR12" s="1">
+        <f t="shared" si="17"/>
+        <v>0.91492463199584084</v>
+      </c>
+      <c r="CS12" s="1">
+        <f t="shared" si="17"/>
+        <v>0.90577538567588245</v>
+      </c>
+      <c r="CT12" s="1">
+        <f t="shared" si="17"/>
+        <v>0.89671763181912356</v>
+      </c>
+      <c r="CU12" s="1">
+        <f t="shared" si="17"/>
+        <v>0.88775045550093235</v>
+      </c>
+      <c r="CV12" s="1">
+        <f t="shared" si="17"/>
+        <v>0.87887295094592299</v>
+      </c>
+      <c r="CW12" s="1">
+        <f t="shared" si="17"/>
+        <v>0.8700842214364638</v>
+      </c>
+      <c r="CX12" s="1">
+        <f t="shared" si="17"/>
+        <v>0.86138337922209918</v>
+      </c>
+      <c r="CY12" s="1">
+        <f t="shared" si="17"/>
+        <v>0.85276954542987815</v>
+      </c>
+      <c r="CZ12" s="1">
+        <f t="shared" ref="CZ12:EI12" si="18">CY12*(1+$AO$17)</f>
+        <v>0.84424184997557938</v>
+      </c>
+      <c r="DA12" s="1">
         <f t="shared" si="18"/>
-        <v>1.2885744462917068</v>
-      </c>
-      <c r="AP12" s="1">
+        <v>0.83579943147582358</v>
+      </c>
+      <c r="DB12" s="1">
         <f t="shared" si="18"/>
-        <v>1.2756887018287897</v>
-      </c>
-      <c r="AQ12" s="1">
+        <v>0.82744143716106533</v>
+      </c>
+      <c r="DC12" s="1">
         <f t="shared" si="18"/>
-        <v>1.2629318148105018</v>
-      </c>
-      <c r="AR12" s="1">
+        <v>0.81916702278945464</v>
+      </c>
+      <c r="DD12" s="1">
         <f t="shared" si="18"/>
-        <v>1.2503024966623968</v>
-      </c>
-      <c r="AS12" s="1">
+        <v>0.81097535256156006</v>
+      </c>
+      <c r="DE12" s="1">
         <f t="shared" si="18"/>
-        <v>1.2377994716957728</v>
-      </c>
-      <c r="AT12" s="1">
+        <v>0.80286559903594445</v>
+      </c>
+      <c r="DF12" s="1">
         <f t="shared" si="18"/>
-        <v>1.225421476978815</v>
-      </c>
-      <c r="AU12" s="1">
+        <v>0.79483694304558505</v>
+      </c>
+      <c r="DG12" s="1">
         <f t="shared" si="18"/>
-        <v>1.2131672622090268</v>
-      </c>
-      <c r="AV12" s="1">
+        <v>0.78688857361512921</v>
+      </c>
+      <c r="DH12" s="1">
         <f t="shared" si="18"/>
-        <v>1.2010355895869365</v>
-      </c>
-      <c r="AW12" s="1">
+        <v>0.77901968787897791</v>
+      </c>
+      <c r="DI12" s="1">
         <f t="shared" si="18"/>
-        <v>1.1890252336910672</v>
-      </c>
-      <c r="AX12" s="1">
+        <v>0.77122949100018812</v>
+      </c>
+      <c r="DJ12" s="1">
         <f t="shared" si="18"/>
-        <v>1.1771349813541565</v>
-      </c>
-      <c r="AY12" s="1">
+        <v>0.7635171960901862</v>
+      </c>
+      <c r="DK12" s="1">
         <f t="shared" si="18"/>
-        <v>1.1653636315406148</v>
-      </c>
-      <c r="AZ12" s="1">
+        <v>0.75588202412928429</v>
+      </c>
+      <c r="DL12" s="1">
         <f t="shared" si="18"/>
-        <v>1.1537099952252088</v>
-      </c>
-      <c r="BA12" s="1">
+        <v>0.74832320388799145</v>
+      </c>
+      <c r="DM12" s="1">
         <f t="shared" si="18"/>
-        <v>1.1421728952729566</v>
-      </c>
-      <c r="BB12" s="1">
+        <v>0.74083997184911154</v>
+      </c>
+      <c r="DN12" s="1">
         <f t="shared" si="18"/>
-        <v>1.130751166320227</v>
-      </c>
-      <c r="BC12" s="1">
+        <v>0.73343157213062038</v>
+      </c>
+      <c r="DO12" s="1">
         <f t="shared" si="18"/>
-        <v>1.1194436546570248</v>
-      </c>
-      <c r="BD12" s="1">
+        <v>0.72609725640931422</v>
+      </c>
+      <c r="DP12" s="1">
         <f t="shared" si="18"/>
-        <v>1.1082492181104546</v>
-      </c>
-      <c r="BE12" s="1">
+        <v>0.71883628384522102</v>
+      </c>
+      <c r="DQ12" s="1">
         <f t="shared" si="18"/>
-        <v>1.0971667259293501</v>
-      </c>
-      <c r="BF12" s="1">
+        <v>0.71164792100676877</v>
+      </c>
+      <c r="DR12" s="1">
         <f t="shared" si="18"/>
-        <v>1.0861950586700566</v>
-      </c>
-      <c r="BG12" s="1">
+        <v>0.70453144179670113</v>
+      </c>
+      <c r="DS12" s="1">
         <f t="shared" si="18"/>
-        <v>1.0753331080833561</v>
-      </c>
-      <c r="BH12" s="1">
+        <v>0.69748612737873417</v>
+      </c>
+      <c r="DT12" s="1">
         <f t="shared" si="18"/>
-        <v>1.0645797770025225</v>
-      </c>
-      <c r="BI12" s="1">
+        <v>0.69051126610494684</v>
+      </c>
+      <c r="DU12" s="1">
         <f t="shared" si="18"/>
-        <v>1.0539339792324973</v>
-      </c>
-      <c r="BJ12" s="1">
+        <v>0.68360615344389741</v>
+      </c>
+      <c r="DV12" s="1">
         <f t="shared" si="18"/>
-        <v>1.0433946394401723</v>
-      </c>
-      <c r="BK12" s="1">
+        <v>0.67677009190945847</v>
+      </c>
+      <c r="DW12" s="1">
         <f t="shared" si="18"/>
-        <v>1.0329606930457707</v>
-      </c>
-      <c r="BL12" s="1">
+        <v>0.67000239099036385</v>
+      </c>
+      <c r="DX12" s="1">
         <f t="shared" si="18"/>
-        <v>1.0226310861153129</v>
-      </c>
-      <c r="BM12" s="1">
+        <v>0.6633023670804602</v>
+      </c>
+      <c r="DY12" s="1">
         <f t="shared" si="18"/>
-        <v>1.0124047752541598</v>
-      </c>
-      <c r="BN12" s="1">
+        <v>0.65666934340965555</v>
+      </c>
+      <c r="DZ12" s="1">
         <f t="shared" si="18"/>
-        <v>1.0022807275016183</v>
-      </c>
-      <c r="BO12" s="1">
+        <v>0.650102649975559</v>
+      </c>
+      <c r="EA12" s="1">
         <f t="shared" si="18"/>
-        <v>0.9922579202266022</v>
-      </c>
-      <c r="BP12" s="1">
+        <v>0.64360162347580341</v>
+      </c>
+      <c r="EB12" s="1">
         <f t="shared" si="18"/>
-        <v>0.98233534102433617</v>
-      </c>
-      <c r="BQ12" s="1">
+        <v>0.63716560724104532</v>
+      </c>
+      <c r="EC12" s="1">
         <f t="shared" si="18"/>
-        <v>0.97251198761409285</v>
-      </c>
-      <c r="BR12" s="1">
+        <v>0.6307939511686349</v>
+      </c>
+      <c r="ED12" s="1">
         <f t="shared" si="18"/>
-        <v>0.96278686773795197</v>
-      </c>
-      <c r="BS12" s="1">
+        <v>0.6244860116569485</v>
+      </c>
+      <c r="EE12" s="1">
         <f t="shared" si="18"/>
-        <v>0.95315899906057244</v>
-      </c>
-      <c r="BT12" s="1">
+        <v>0.61824115154037906</v>
+      </c>
+      <c r="EF12" s="1">
         <f t="shared" si="18"/>
-        <v>0.94362740906996667</v>
-      </c>
-      <c r="BU12" s="1">
+        <v>0.61205874002497529</v>
+      </c>
+      <c r="EG12" s="1">
         <f t="shared" si="18"/>
-        <v>0.93419113497926698</v>
-      </c>
-      <c r="BV12" s="1">
+        <v>0.6059381526247255</v>
+      </c>
+      <c r="EH12" s="1">
         <f t="shared" si="18"/>
-        <v>0.9248492236294743</v>
-      </c>
-      <c r="BW12" s="1">
+        <v>0.5998787710984782</v>
+      </c>
+      <c r="EI12" s="1">
         <f t="shared" si="18"/>
-        <v>0.91560073139317955</v>
-      </c>
-      <c r="BX12" s="1">
-        <f t="shared" si="18"/>
-        <v>0.9064447240792477</v>
-      </c>
-      <c r="BY12" s="1">
-        <f t="shared" si="18"/>
-        <v>0.89738027683845523</v>
-      </c>
-      <c r="BZ12" s="1">
-        <f t="shared" si="18"/>
-        <v>0.88840647407007067</v>
-      </c>
-      <c r="CA12" s="1">
-        <f t="shared" si="18"/>
-        <v>0.87952240932936998</v>
-      </c>
-      <c r="CB12" s="1">
-        <f t="shared" si="18"/>
-        <v>0.87072718523607628</v>
-      </c>
-      <c r="CC12" s="1">
-        <f t="shared" si="18"/>
-        <v>0.86201991338371553</v>
-      </c>
-      <c r="CD12" s="1">
-        <f t="shared" si="18"/>
-        <v>0.85339971424987837</v>
-      </c>
-      <c r="CE12" s="1">
-        <f t="shared" si="18"/>
-        <v>0.84486571710737957</v>
-      </c>
-      <c r="CF12" s="1">
-        <f t="shared" si="18"/>
-        <v>0.83641705993630577</v>
-      </c>
-      <c r="CG12" s="1">
-        <f t="shared" si="18"/>
-        <v>0.82805288933694265</v>
-      </c>
-      <c r="CH12" s="1">
-        <f t="shared" si="18"/>
-        <v>0.81977236044357327</v>
-      </c>
-      <c r="CI12" s="1">
-        <f t="shared" si="18"/>
-        <v>0.81157463683913755</v>
-      </c>
-      <c r="CJ12" s="1">
-        <f t="shared" si="18"/>
-        <v>0.80345889047074615</v>
-      </c>
-      <c r="CK12" s="1">
-        <f t="shared" si="18"/>
-        <v>0.79542430156603872</v>
-      </c>
-      <c r="CL12" s="1">
-        <f t="shared" si="18"/>
-        <v>0.78747005855037833</v>
-      </c>
-      <c r="CM12" s="1">
-        <f t="shared" si="18"/>
-        <v>0.77959535796487456</v>
-      </c>
-      <c r="CN12" s="1">
-        <f t="shared" si="18"/>
-        <v>0.77179940438522576</v>
-      </c>
-      <c r="CO12" s="1">
-        <f t="shared" si="18"/>
-        <v>0.76408141034137345</v>
-      </c>
-      <c r="CP12" s="1">
-        <f t="shared" si="18"/>
-        <v>0.75644059623795967</v>
-      </c>
-      <c r="CQ12" s="1">
-        <f t="shared" si="18"/>
-        <v>0.74887619027558006</v>
-      </c>
-      <c r="CR12" s="1">
-        <f t="shared" si="18"/>
-        <v>0.74138742837282423</v>
-      </c>
-      <c r="CS12" s="1">
-        <f t="shared" si="18"/>
-        <v>0.73397355408909604</v>
-      </c>
-      <c r="CT12" s="1">
-        <f t="shared" si="18"/>
-        <v>0.72663381854820508</v>
-      </c>
-      <c r="CU12" s="1">
-        <f t="shared" si="18"/>
-        <v>0.71936748036272302</v>
-      </c>
-      <c r="CV12" s="1">
-        <f t="shared" si="18"/>
-        <v>0.71217380555909582</v>
-      </c>
-      <c r="CW12" s="1">
-        <f t="shared" si="18"/>
-        <v>0.70505206750350491</v>
-      </c>
-      <c r="CX12" s="1">
-        <f t="shared" si="18"/>
-        <v>0.69800154682846982</v>
-      </c>
-      <c r="CY12" s="1">
-        <f t="shared" si="18"/>
-        <v>0.69102153136018507</v>
-      </c>
-      <c r="CZ12" s="1">
-        <f t="shared" ref="CZ12:EI12" si="19">CY12*(1+$AO$17)</f>
-        <v>0.68411131604658326</v>
-      </c>
-      <c r="DA12" s="1">
-        <f t="shared" si="19"/>
-        <v>0.67727020288611739</v>
-      </c>
-      <c r="DB12" s="1">
-        <f t="shared" si="19"/>
-        <v>0.67049750085725623</v>
-      </c>
-      <c r="DC12" s="1">
-        <f t="shared" si="19"/>
-        <v>0.66379252584868365</v>
-      </c>
-      <c r="DD12" s="1">
-        <f t="shared" si="19"/>
-        <v>0.65715460059019681</v>
-      </c>
-      <c r="DE12" s="1">
-        <f t="shared" si="19"/>
-        <v>0.65058305458429488</v>
-      </c>
-      <c r="DF12" s="1">
-        <f t="shared" si="19"/>
-        <v>0.64407722403845191</v>
-      </c>
-      <c r="DG12" s="1">
-        <f t="shared" si="19"/>
-        <v>0.63763645179806738</v>
-      </c>
-      <c r="DH12" s="1">
-        <f t="shared" si="19"/>
-        <v>0.63126008728008676</v>
-      </c>
-      <c r="DI12" s="1">
-        <f t="shared" si="19"/>
-        <v>0.62494748640728592</v>
-      </c>
-      <c r="DJ12" s="1">
-        <f t="shared" si="19"/>
-        <v>0.61869801154321302</v>
-      </c>
-      <c r="DK12" s="1">
-        <f t="shared" si="19"/>
-        <v>0.61251103142778085</v>
-      </c>
-      <c r="DL12" s="1">
-        <f t="shared" si="19"/>
-        <v>0.60638592111350309</v>
-      </c>
-      <c r="DM12" s="1">
-        <f t="shared" si="19"/>
-        <v>0.60032206190236803</v>
-      </c>
-      <c r="DN12" s="1">
-        <f t="shared" si="19"/>
-        <v>0.59431884128334433</v>
-      </c>
-      <c r="DO12" s="1">
-        <f t="shared" si="19"/>
-        <v>0.58837565287051086</v>
-      </c>
-      <c r="DP12" s="1">
-        <f t="shared" si="19"/>
-        <v>0.58249189634180576</v>
-      </c>
-      <c r="DQ12" s="1">
-        <f t="shared" si="19"/>
-        <v>0.57666697737838768</v>
-      </c>
-      <c r="DR12" s="1">
-        <f t="shared" si="19"/>
-        <v>0.57090030760460375</v>
-      </c>
-      <c r="DS12" s="1">
-        <f t="shared" si="19"/>
-        <v>0.5651913045285577</v>
-      </c>
-      <c r="DT12" s="1">
-        <f t="shared" si="19"/>
-        <v>0.55953939148327214</v>
-      </c>
-      <c r="DU12" s="1">
-        <f t="shared" si="19"/>
-        <v>0.55394399756843937</v>
-      </c>
-      <c r="DV12" s="1">
-        <f t="shared" si="19"/>
-        <v>0.54840455759275497</v>
-      </c>
-      <c r="DW12" s="1">
-        <f t="shared" si="19"/>
-        <v>0.54292051201682745</v>
-      </c>
-      <c r="DX12" s="1">
-        <f t="shared" si="19"/>
-        <v>0.53749130689665914</v>
-      </c>
-      <c r="DY12" s="1">
-        <f t="shared" si="19"/>
-        <v>0.53211639382769249</v>
-      </c>
-      <c r="DZ12" s="1">
-        <f t="shared" si="19"/>
-        <v>0.52679522988941552</v>
-      </c>
-      <c r="EA12" s="1">
-        <f t="shared" si="19"/>
-        <v>0.52152727759052131</v>
-      </c>
-      <c r="EB12" s="1">
-        <f t="shared" si="19"/>
-        <v>0.51631200481461614</v>
-      </c>
-      <c r="EC12" s="1">
-        <f t="shared" si="19"/>
-        <v>0.51114888476647002</v>
-      </c>
-      <c r="ED12" s="1">
-        <f t="shared" si="19"/>
-        <v>0.50603739591880537</v>
-      </c>
-      <c r="EE12" s="1">
-        <f t="shared" si="19"/>
-        <v>0.50097702195961735</v>
-      </c>
-      <c r="EF12" s="1">
-        <f t="shared" si="19"/>
-        <v>0.49596725174002115</v>
-      </c>
-      <c r="EG12" s="1">
-        <f t="shared" si="19"/>
-        <v>0.49100757922262095</v>
-      </c>
-      <c r="EH12" s="1">
-        <f t="shared" si="19"/>
-        <v>0.48609750343039476</v>
-      </c>
-      <c r="EI12" s="1">
-        <f t="shared" si="19"/>
-        <v>0.48123652839609082</v>
+        <v>0.59387998338749337</v>
       </c>
     </row>
     <row r="13" spans="2:139" x14ac:dyDescent="0.3">
@@ -2842,144 +2839,144 @@
         <v>29</v>
       </c>
       <c r="C14" s="5">
-        <f t="shared" ref="C14:S14" si="20">C12/C13</f>
+        <f t="shared" ref="C14:S14" si="19">C12/C13</f>
         <v>2.1276595744680705E-2</v>
       </c>
       <c r="D14" s="5">
+        <f t="shared" si="19"/>
+        <v>5.3191489361702128E-2</v>
+      </c>
+      <c r="E14" s="5">
+        <f t="shared" si="19"/>
+        <v>-5.3191489361702114E-2</v>
+      </c>
+      <c r="F14" s="5">
+        <f t="shared" si="19"/>
+        <v>3.191489361702133E-2</v>
+      </c>
+      <c r="G14" s="5">
+        <f t="shared" si="19"/>
+        <v>-1.0638297872340373E-2</v>
+      </c>
+      <c r="H14" s="5">
+        <f t="shared" si="19"/>
+        <v>6.3829787234042604E-2</v>
+      </c>
+      <c r="I14" s="5">
+        <f t="shared" si="19"/>
+        <v>3.1914893617021212E-2</v>
+      </c>
+      <c r="J14" s="5">
+        <f t="shared" si="19"/>
+        <v>4.2553191489361694E-2</v>
+      </c>
+      <c r="K14" s="5">
+        <f t="shared" si="19"/>
+        <v>1.053191489361702</v>
+      </c>
+      <c r="L14" s="5">
+        <f t="shared" si="19"/>
+        <v>-0.11702127659574468</v>
+      </c>
+      <c r="M14" s="5">
+        <f t="shared" si="19"/>
+        <v>-2.1276595744680864E-2</v>
+      </c>
+      <c r="N14" s="5">
+        <f t="shared" si="19"/>
+        <v>-3.1914893617021232E-2</v>
+      </c>
+      <c r="O14" s="5">
+        <f t="shared" si="19"/>
+        <v>-2.1505376344086009E-2</v>
+      </c>
+      <c r="P14" s="5">
+        <f t="shared" si="19"/>
+        <v>-3.1914893617021274E-2</v>
+      </c>
+      <c r="Q14" s="5">
+        <f t="shared" si="19"/>
+        <v>-4.2553191489361694E-2</v>
+      </c>
+      <c r="R14" s="5">
+        <f t="shared" si="19"/>
+        <v>-1.0638297872340429E-2</v>
+      </c>
+      <c r="S14" s="5">
+        <f t="shared" si="19"/>
+        <v>-4.2553191489361687E-2</v>
+      </c>
+      <c r="T14" s="5">
+        <f t="shared" ref="T14:V14" si="20">T12/T13</f>
+        <v>1.0638297872340417E-2</v>
+      </c>
+      <c r="U14" s="5">
         <f t="shared" si="20"/>
-        <v>5.3191489361702128E-2</v>
-      </c>
-      <c r="E14" s="5">
+        <v>-3.1914893617021295E-2</v>
+      </c>
+      <c r="V14" s="5">
         <f t="shared" si="20"/>
-        <v>-5.3191489361702114E-2</v>
-      </c>
-      <c r="F14" s="5">
-        <f t="shared" si="20"/>
-        <v>3.191489361702133E-2</v>
-      </c>
-      <c r="G14" s="5">
-        <f t="shared" si="20"/>
-        <v>-1.0638297872340373E-2</v>
-      </c>
-      <c r="H14" s="5">
-        <f t="shared" si="20"/>
-        <v>6.3829787234042604E-2</v>
-      </c>
-      <c r="I14" s="5">
-        <f t="shared" si="20"/>
-        <v>3.1914893617021212E-2</v>
-      </c>
-      <c r="J14" s="5">
-        <f t="shared" si="20"/>
-        <v>4.2553191489361694E-2</v>
-      </c>
-      <c r="K14" s="5">
-        <f t="shared" si="20"/>
-        <v>1.053191489361702</v>
-      </c>
-      <c r="L14" s="5">
-        <f t="shared" si="20"/>
-        <v>-0.11702127659574468</v>
-      </c>
-      <c r="M14" s="5">
-        <f t="shared" si="20"/>
-        <v>-2.1276595744680864E-2</v>
-      </c>
-      <c r="N14" s="5">
-        <f t="shared" si="20"/>
-        <v>-3.1914893617021232E-2</v>
-      </c>
-      <c r="O14" s="5">
-        <f t="shared" si="20"/>
-        <v>-2.1505376344086009E-2</v>
-      </c>
-      <c r="P14" s="5">
-        <f t="shared" si="20"/>
-        <v>-3.1914893617021274E-2</v>
-      </c>
-      <c r="Q14" s="5">
-        <f t="shared" si="20"/>
-        <v>-4.2553191489361694E-2</v>
-      </c>
-      <c r="R14" s="5">
-        <f t="shared" si="20"/>
-        <v>-1.0638297872340429E-2</v>
-      </c>
-      <c r="S14" s="5">
-        <f t="shared" si="20"/>
-        <v>-4.2553191489361687E-2</v>
-      </c>
-      <c r="T14" s="5">
-        <f t="shared" ref="T14:V14" si="21">T12/T13</f>
-        <v>1.0638297872340417E-2</v>
-      </c>
-      <c r="U14" s="5">
+        <v>-1.232978723404256E-2</v>
+      </c>
+      <c r="X14" s="5">
+        <f t="shared" ref="X14:AC14" si="21">X12/X13</f>
+        <v>5.3763440860215013E-2</v>
+      </c>
+      <c r="Y14" s="5">
         <f t="shared" si="21"/>
-        <v>-2.6627659574468075E-2</v>
-      </c>
-      <c r="V14" s="5">
+        <v>0.13978494623655927</v>
+      </c>
+      <c r="Z14" s="5">
         <f t="shared" si="21"/>
-        <v>-8.7712765957446651E-3</v>
-      </c>
-      <c r="X14" s="5">
-        <f t="shared" ref="X14:AC14" si="22">X12/X13</f>
-        <v>5.3763440860215013E-2</v>
-      </c>
-      <c r="Y14" s="5">
+        <v>0.90322580645161266</v>
+      </c>
+      <c r="AA14" s="5">
+        <f t="shared" si="21"/>
+        <v>-0.10752688172042994</v>
+      </c>
+      <c r="AB14" s="5">
+        <f t="shared" si="21"/>
+        <v>-7.615957446808512E-2</v>
+      </c>
+      <c r="AC14" s="5">
+        <f t="shared" si="21"/>
+        <v>-3.1065319148936146E-2</v>
+      </c>
+      <c r="AD14" s="5">
+        <f t="shared" ref="AD14:AL14" si="22">AD12/AD13</f>
+        <v>-2.6017021276566726E-5</v>
+      </c>
+      <c r="AE14" s="5">
         <f t="shared" si="22"/>
-        <v>0.13978494623655927</v>
-      </c>
-      <c r="Z14" s="5">
+        <v>2.6030079063829814E-2</v>
+      </c>
+      <c r="AF14" s="5">
         <f t="shared" si="22"/>
-        <v>0.90322580645161266</v>
-      </c>
-      <c r="AA14" s="5">
+        <v>4.6555355772766024E-2</v>
+      </c>
+      <c r="AG14" s="5">
         <f t="shared" si="22"/>
-        <v>-0.10752688172042994</v>
-      </c>
-      <c r="AB14" s="5">
+        <v>6.7291091264604266E-2</v>
+      </c>
+      <c r="AH14" s="5">
         <f t="shared" si="22"/>
-        <v>-6.7313829787233895E-2</v>
-      </c>
-      <c r="AC14" s="5">
+        <v>8.8243495182515605E-2</v>
+      </c>
+      <c r="AI14" s="5">
         <f t="shared" si="22"/>
-        <v>-3.7741755319148737E-2</v>
-      </c>
-      <c r="AD14" s="5">
-        <f t="shared" ref="AD14:AL14" si="23">AD12/AD13</f>
-        <v>-1.8638664893616905E-2</v>
-      </c>
-      <c r="AE14" s="5">
-        <f t="shared" si="23"/>
-        <v>6.4790808510645107E-4</v>
-      </c>
-      <c r="AF14" s="5">
-        <f t="shared" si="23"/>
-        <v>2.0123619060638458E-2</v>
-      </c>
-      <c r="AG14" s="5">
-        <f t="shared" si="23"/>
-        <v>3.9794216727542686E-2</v>
-      </c>
-      <c r="AH14" s="5">
-        <f t="shared" si="23"/>
-        <v>5.9665545094928149E-2</v>
-      </c>
-      <c r="AI14" s="5">
-        <f t="shared" si="23"/>
-        <v>7.9743545589333109E-2</v>
+        <v>0.10941888135785884</v>
       </c>
       <c r="AJ14" s="5">
-        <f t="shared" si="23"/>
-        <v>0.1000342591977009</v>
+        <f t="shared" si="22"/>
+        <v>0.13082367009399207</v>
       </c>
       <c r="AK14" s="5">
-        <f t="shared" si="23"/>
-        <v>0.12054382865127025</v>
+        <f t="shared" si="22"/>
+        <v>0.15246439049375826</v>
       </c>
       <c r="AL14" s="5">
-        <f t="shared" si="23"/>
-        <v>0.14127850065121481</v>
+        <f t="shared" si="22"/>
+        <v>0.17434768283154084</v>
       </c>
     </row>
     <row r="16" spans="2:139" x14ac:dyDescent="0.3">
@@ -2991,39 +2988,39 @@
       <c r="E16" s="10"/>
       <c r="F16" s="10"/>
       <c r="G16" s="10">
-        <f t="shared" ref="G16:O16" si="24">G3/C3-1</f>
+        <f t="shared" ref="G16:O16" si="23">G3/C3-1</f>
         <v>-0.15384615384615363</v>
       </c>
       <c r="H16" s="10">
-        <f t="shared" si="24"/>
+        <f t="shared" si="23"/>
         <v>-0.10204081632653061</v>
       </c>
       <c r="I16" s="10">
-        <f t="shared" si="24"/>
+        <f t="shared" si="23"/>
         <v>0.14999999999999991</v>
       </c>
       <c r="J16" s="10">
-        <f t="shared" si="24"/>
+        <f t="shared" si="23"/>
         <v>-0.22222222222222221</v>
       </c>
       <c r="K16" s="10">
-        <f t="shared" si="24"/>
+        <f t="shared" si="23"/>
         <v>-0.2272727272727274</v>
       </c>
       <c r="L16" s="10">
-        <f t="shared" si="24"/>
+        <f t="shared" si="23"/>
         <v>-0.25000000000000011</v>
       </c>
       <c r="M16" s="10">
-        <f t="shared" si="24"/>
+        <f t="shared" si="23"/>
         <v>-0.26086956521739124</v>
       </c>
       <c r="N16" s="10">
-        <f t="shared" si="24"/>
+        <f t="shared" si="23"/>
         <v>-0.26190476190476186</v>
       </c>
       <c r="O16" s="10">
-        <f t="shared" si="24"/>
+        <f t="shared" si="23"/>
         <v>0</v>
       </c>
       <c r="P16" s="10">
@@ -3031,28 +3028,28 @@
         <v>3.0303030303030276E-2</v>
       </c>
       <c r="Q16" s="10">
-        <f t="shared" ref="Q16:V16" si="25">Q3/M3-1</f>
+        <f t="shared" ref="Q16:V16" si="24">Q3/M3-1</f>
         <v>-0.23529411764705876</v>
       </c>
       <c r="R16" s="10">
-        <f t="shared" si="25"/>
+        <f t="shared" si="24"/>
         <v>-6.4516129032258118E-2</v>
       </c>
       <c r="S16" s="10">
-        <f t="shared" si="25"/>
+        <f t="shared" si="24"/>
         <v>-5.8823529411764608E-2</v>
       </c>
       <c r="T16" s="10">
-        <f t="shared" si="25"/>
+        <f t="shared" si="24"/>
         <v>5.8823529411764719E-2</v>
       </c>
       <c r="U16" s="10">
-        <f t="shared" si="25"/>
-        <v>5.0000000000000044E-2</v>
+        <f t="shared" si="24"/>
+        <v>7.6923076923076872E-2</v>
       </c>
       <c r="V16" s="10">
-        <f t="shared" si="25"/>
-        <v>5.0000000000000044E-2</v>
+        <f t="shared" si="24"/>
+        <v>0.10000000000000009</v>
       </c>
       <c r="X16" s="10"/>
       <c r="Y16" s="10">
@@ -3060,55 +3057,55 @@
         <v>-9.7435897435897312E-2</v>
       </c>
       <c r="Z16" s="10">
-        <f t="shared" ref="Z16:AL16" si="26">Z3/Y3-1</f>
+        <f t="shared" ref="Z16:AL16" si="25">Z3/Y3-1</f>
         <v>-0.25568181818181823</v>
       </c>
       <c r="AA16" s="10">
-        <f t="shared" si="26"/>
+        <f t="shared" si="25"/>
         <v>-6.1068702290076216E-2</v>
       </c>
       <c r="AB16" s="10">
-        <f t="shared" si="26"/>
-        <v>2.2357723577235866E-2</v>
+        <f t="shared" si="25"/>
+        <v>3.9837398373983701E-2</v>
       </c>
       <c r="AC16" s="10">
-        <f t="shared" si="26"/>
+        <f t="shared" si="25"/>
+        <v>6.0000000000000053E-2</v>
+      </c>
+      <c r="AD16" s="10">
+        <f t="shared" si="25"/>
+        <v>4.0000000000000036E-2</v>
+      </c>
+      <c r="AE16" s="10">
+        <f t="shared" si="25"/>
         <v>3.0000000000000027E-2</v>
       </c>
-      <c r="AD16" s="10">
-        <f t="shared" si="26"/>
+      <c r="AF16" s="10">
+        <f t="shared" si="25"/>
         <v>2.0000000000000018E-2</v>
       </c>
-      <c r="AE16" s="10">
-        <f t="shared" si="26"/>
+      <c r="AG16" s="10">
+        <f t="shared" si="25"/>
         <v>2.0000000000000018E-2</v>
       </c>
-      <c r="AF16" s="10">
-        <f t="shared" si="26"/>
+      <c r="AH16" s="10">
+        <f t="shared" si="25"/>
         <v>2.0000000000000018E-2</v>
       </c>
-      <c r="AG16" s="10">
-        <f t="shared" si="26"/>
+      <c r="AI16" s="10">
+        <f t="shared" si="25"/>
         <v>2.0000000000000018E-2</v>
       </c>
-      <c r="AH16" s="10">
-        <f t="shared" si="26"/>
+      <c r="AJ16" s="10">
+        <f t="shared" si="25"/>
         <v>2.0000000000000018E-2</v>
       </c>
-      <c r="AI16" s="10">
-        <f t="shared" si="26"/>
+      <c r="AK16" s="10">
+        <f t="shared" si="25"/>
         <v>2.0000000000000018E-2</v>
       </c>
-      <c r="AJ16" s="10">
-        <f t="shared" si="26"/>
-        <v>2.0000000000000018E-2</v>
-      </c>
-      <c r="AK16" s="10">
-        <f t="shared" si="26"/>
-        <v>2.0000000000000018E-2</v>
-      </c>
       <c r="AL16" s="10">
-        <f t="shared" si="26"/>
+        <f t="shared" si="25"/>
         <v>2.0000000000000018E-2</v>
       </c>
     </row>
@@ -3117,55 +3114,55 @@
         <v>35</v>
       </c>
       <c r="C17" s="10">
-        <f t="shared" ref="C17:O17" si="27">C5/C3</f>
+        <f t="shared" ref="C17:O17" si="26">C5/C3</f>
         <v>0.32692307692307676</v>
       </c>
       <c r="D17" s="10">
-        <f t="shared" si="27"/>
+        <f t="shared" si="26"/>
         <v>0.32653061224489804</v>
       </c>
       <c r="E17" s="10">
-        <f t="shared" si="27"/>
+        <f t="shared" si="26"/>
         <v>0.35</v>
       </c>
       <c r="F17" s="10">
-        <f t="shared" si="27"/>
+        <f t="shared" si="26"/>
         <v>0.37037037037037041</v>
       </c>
       <c r="G17" s="10">
-        <f t="shared" si="27"/>
+        <f t="shared" si="26"/>
         <v>0.3636363636363637</v>
       </c>
       <c r="H17" s="10">
-        <f t="shared" si="27"/>
+        <f t="shared" si="26"/>
         <v>0.34090909090909099</v>
       </c>
       <c r="I17" s="10">
-        <f t="shared" si="27"/>
+        <f t="shared" si="26"/>
         <v>0.41304347826086946</v>
       </c>
       <c r="J17" s="10">
-        <f t="shared" si="27"/>
+        <f t="shared" si="26"/>
         <v>0.35714285714285715</v>
       </c>
       <c r="K17" s="10">
-        <f t="shared" si="27"/>
+        <f t="shared" si="26"/>
         <v>0.35294117647058815</v>
       </c>
       <c r="L17" s="10">
-        <f t="shared" si="27"/>
+        <f t="shared" si="26"/>
         <v>0.36363636363636359</v>
       </c>
       <c r="M17" s="10">
-        <f t="shared" si="27"/>
+        <f t="shared" si="26"/>
         <v>0.38235294117647056</v>
       </c>
       <c r="N17" s="10">
-        <f t="shared" si="27"/>
+        <f t="shared" si="26"/>
         <v>0.25806451612903236</v>
       </c>
       <c r="O17" s="10">
-        <f t="shared" si="27"/>
+        <f t="shared" si="26"/>
         <v>0.3235294117647059</v>
       </c>
       <c r="P17" s="10">
@@ -3173,87 +3170,87 @@
         <v>0.3235294117647059</v>
       </c>
       <c r="Q17" s="10">
-        <f t="shared" ref="Q17:V17" si="28">Q5/Q3</f>
+        <f t="shared" ref="Q17:V17" si="27">Q5/Q3</f>
         <v>0.30769230769230771</v>
       </c>
       <c r="R17" s="10">
-        <f t="shared" si="28"/>
+        <f t="shared" si="27"/>
         <v>0.41379310344827586</v>
       </c>
       <c r="S17" s="10">
-        <f t="shared" si="28"/>
+        <f t="shared" si="27"/>
         <v>0.37500000000000006</v>
       </c>
       <c r="T17" s="10">
-        <f t="shared" si="28"/>
+        <f t="shared" si="27"/>
         <v>0.38888888888888884</v>
       </c>
       <c r="U17" s="10">
-        <f t="shared" si="28"/>
+        <f t="shared" si="27"/>
+        <v>0.39285714285714285</v>
+      </c>
+      <c r="V17" s="10">
+        <f t="shared" si="27"/>
         <v>0.39</v>
       </c>
-      <c r="V17" s="10">
-        <f t="shared" si="28"/>
-        <v>0.39000000000000007</v>
-      </c>
       <c r="X17" s="10">
-        <f t="shared" ref="X17" si="29">X5/X3</f>
+        <f t="shared" ref="X17" si="28">X5/X3</f>
         <v>0.34358974358974353</v>
       </c>
       <c r="Y17" s="10">
-        <f t="shared" ref="Y17:AL17" si="30">Y5/Y3</f>
+        <f t="shared" ref="Y17:AL17" si="29">Y5/Y3</f>
         <v>0.37500000000000006</v>
       </c>
       <c r="Z17" s="10">
-        <f t="shared" si="30"/>
+        <f t="shared" si="29"/>
         <v>0.34351145038167941</v>
       </c>
       <c r="AA17" s="10">
-        <f t="shared" si="30"/>
+        <f t="shared" si="29"/>
         <v>0.34146341463414642</v>
       </c>
       <c r="AB17" s="10">
-        <f t="shared" si="30"/>
-        <v>0.38586481113320081</v>
+        <f t="shared" si="29"/>
+        <v>0.38655981235340109</v>
       </c>
       <c r="AC17" s="10">
-        <f t="shared" si="30"/>
+        <f t="shared" si="29"/>
         <v>0.39</v>
       </c>
       <c r="AD17" s="10">
-        <f t="shared" si="30"/>
+        <f t="shared" si="29"/>
         <v>0.39</v>
       </c>
       <c r="AE17" s="10">
-        <f t="shared" si="30"/>
-        <v>0.38999999999999996</v>
+        <f t="shared" si="29"/>
+        <v>0.39</v>
       </c>
       <c r="AF17" s="10">
-        <f t="shared" si="30"/>
+        <f t="shared" si="29"/>
         <v>0.39</v>
       </c>
       <c r="AG17" s="10">
-        <f t="shared" si="30"/>
+        <f t="shared" si="29"/>
         <v>0.39</v>
       </c>
       <c r="AH17" s="10">
-        <f t="shared" si="30"/>
-        <v>0.38999999999999996</v>
+        <f t="shared" si="29"/>
+        <v>0.39</v>
       </c>
       <c r="AI17" s="10">
-        <f t="shared" si="30"/>
-        <v>0.39000000000000007</v>
+        <f t="shared" si="29"/>
+        <v>0.39</v>
       </c>
       <c r="AJ17" s="10">
-        <f t="shared" si="30"/>
+        <f t="shared" si="29"/>
         <v>0.39</v>
       </c>
       <c r="AK17" s="10">
-        <f t="shared" si="30"/>
+        <f t="shared" si="29"/>
         <v>0.39</v>
       </c>
       <c r="AL17" s="10">
-        <f t="shared" si="30"/>
+        <f t="shared" si="29"/>
         <v>0.39</v>
       </c>
       <c r="AN17" t="s">
@@ -3272,39 +3269,39 @@
       <c r="E18" s="10"/>
       <c r="F18" s="10"/>
       <c r="G18" s="10">
-        <f t="shared" ref="G18:O18" si="31">G6/C6-1</f>
+        <f t="shared" ref="G18:O18" si="30">G6/C6-1</f>
         <v>0.19999999999999996</v>
       </c>
       <c r="H18" s="10">
-        <f t="shared" si="31"/>
+        <f t="shared" si="30"/>
         <v>-0.25000000000000011</v>
       </c>
       <c r="I18" s="10">
-        <f t="shared" si="31"/>
+        <f t="shared" si="30"/>
         <v>-0.30434782608695643</v>
       </c>
       <c r="J18" s="10">
-        <f t="shared" si="31"/>
+        <f t="shared" si="30"/>
         <v>-0.3529411764705882</v>
       </c>
       <c r="K18" s="10">
-        <f t="shared" si="31"/>
+        <f t="shared" si="30"/>
         <v>12.166666666666666</v>
       </c>
       <c r="L18" s="10">
-        <f t="shared" si="31"/>
+        <f t="shared" si="30"/>
         <v>1.0833333333333335</v>
       </c>
       <c r="M18" s="10">
-        <f t="shared" si="31"/>
+        <f t="shared" si="30"/>
         <v>6.25E-2</v>
       </c>
       <c r="N18" s="10">
-        <f t="shared" si="31"/>
+        <f t="shared" si="30"/>
         <v>0.27272727272727249</v>
       </c>
       <c r="O18" s="10">
-        <f t="shared" si="31"/>
+        <f t="shared" si="30"/>
         <v>-0.93670886075949367</v>
       </c>
       <c r="P18" s="10">
@@ -3312,28 +3309,28 @@
         <v>-0.36</v>
       </c>
       <c r="Q18" s="10">
-        <f t="shared" ref="Q18:V18" si="32">Q6/M6-1</f>
+        <f t="shared" ref="Q18:V18" si="31">Q6/M6-1</f>
         <v>-0.11764705882352944</v>
       </c>
       <c r="R18" s="10">
-        <f t="shared" si="32"/>
+        <f t="shared" si="31"/>
         <v>7.1428571428571397E-2</v>
       </c>
       <c r="S18" s="10">
-        <f t="shared" si="32"/>
+        <f t="shared" si="31"/>
         <v>0.19999999999999996</v>
       </c>
       <c r="T18" s="10">
-        <f t="shared" si="32"/>
+        <f t="shared" si="31"/>
         <v>-6.25E-2</v>
       </c>
       <c r="U18" s="10">
-        <f t="shared" si="32"/>
-        <v>1.0000000000000009E-2</v>
+        <f t="shared" si="31"/>
+        <v>6.6666666666666652E-2</v>
       </c>
       <c r="V18" s="10">
-        <f t="shared" si="32"/>
-        <v>-2.0000000000000018E-2</v>
+        <f t="shared" si="31"/>
+        <v>4.0000000000000036E-2</v>
       </c>
       <c r="X18" s="10"/>
       <c r="Y18" s="10">
@@ -3341,62 +3338,62 @@
         <v>-0.19718309859154926</v>
       </c>
       <c r="Z18" s="10">
-        <f t="shared" ref="Z18:AL18" si="33">Z6/Y6-1</f>
+        <f t="shared" ref="Z18:AL18" si="32">Z6/Y6-1</f>
         <v>4.140350877192982</v>
       </c>
       <c r="AA18" s="10">
-        <f t="shared" si="33"/>
+        <f t="shared" si="32"/>
         <v>-0.79180887372013653</v>
       </c>
       <c r="AB18" s="10">
-        <f t="shared" si="33"/>
-        <v>3.0327868852458861E-2</v>
+        <f t="shared" si="32"/>
+        <v>5.9016393442623105E-2</v>
       </c>
       <c r="AC18" s="10">
-        <f t="shared" si="33"/>
+        <f t="shared" si="32"/>
+        <v>-1.000000000000012E-2</v>
+      </c>
+      <c r="AD18" s="10">
+        <f t="shared" si="32"/>
         <v>-1.0000000000000009E-2</v>
       </c>
-      <c r="AD18" s="10">
-        <f t="shared" si="33"/>
+      <c r="AE18" s="10">
+        <f t="shared" si="32"/>
         <v>-1.0000000000000009E-2</v>
       </c>
-      <c r="AE18" s="10">
-        <f t="shared" si="33"/>
+      <c r="AF18" s="10">
+        <f t="shared" si="32"/>
         <v>-1.0000000000000009E-2</v>
       </c>
-      <c r="AF18" s="10">
-        <f t="shared" si="33"/>
+      <c r="AG18" s="10">
+        <f t="shared" si="32"/>
+        <v>-1.0000000000000009E-2</v>
+      </c>
+      <c r="AH18" s="10">
+        <f t="shared" si="32"/>
         <v>-1.000000000000012E-2</v>
       </c>
-      <c r="AG18" s="10">
-        <f t="shared" si="33"/>
+      <c r="AI18" s="10">
+        <f t="shared" si="32"/>
         <v>-1.0000000000000009E-2</v>
       </c>
-      <c r="AH18" s="10">
-        <f t="shared" si="33"/>
+      <c r="AJ18" s="10">
+        <f t="shared" si="32"/>
         <v>-1.0000000000000009E-2</v>
       </c>
-      <c r="AI18" s="10">
-        <f t="shared" si="33"/>
+      <c r="AK18" s="10">
+        <f t="shared" si="32"/>
         <v>-1.000000000000012E-2</v>
       </c>
-      <c r="AJ18" s="10">
-        <f t="shared" si="33"/>
+      <c r="AL18" s="10">
+        <f t="shared" si="32"/>
         <v>-1.0000000000000009E-2</v>
-      </c>
-      <c r="AK18" s="10">
-        <f t="shared" si="33"/>
-        <v>-1.0000000000000009E-2</v>
-      </c>
-      <c r="AL18" s="10">
-        <f t="shared" si="33"/>
-        <v>-9.9999999999998979E-3</v>
       </c>
       <c r="AN18" t="s">
         <v>48</v>
       </c>
       <c r="AO18" s="10">
-        <v>0.12</v>
+        <v>0.13</v>
       </c>
     </row>
     <row r="19" spans="2:41" x14ac:dyDescent="0.3">
@@ -3404,55 +3401,55 @@
         <v>37</v>
       </c>
       <c r="C19" s="10">
-        <f t="shared" ref="C19:O19" si="34">C7/C3</f>
+        <f t="shared" ref="C19:O19" si="33">C7/C3</f>
         <v>3.84615384615382E-2</v>
       </c>
       <c r="D19" s="10">
-        <f t="shared" si="34"/>
+        <f t="shared" si="33"/>
         <v>0</v>
       </c>
       <c r="E19" s="10">
-        <f t="shared" si="34"/>
+        <f t="shared" si="33"/>
         <v>-0.22499999999999998</v>
       </c>
       <c r="F19" s="10">
-        <f t="shared" si="34"/>
+        <f t="shared" si="33"/>
         <v>5.5555555555555643E-2</v>
       </c>
       <c r="G19" s="10">
-        <f t="shared" si="34"/>
+        <f t="shared" si="33"/>
         <v>-4.5454545454545338E-2</v>
       </c>
       <c r="H19" s="10">
-        <f t="shared" si="34"/>
+        <f t="shared" si="33"/>
         <v>6.8181818181818288E-2</v>
       </c>
       <c r="I19" s="10">
-        <f t="shared" si="34"/>
+        <f t="shared" si="33"/>
         <v>6.5217391304347699E-2</v>
       </c>
       <c r="J19" s="10">
-        <f t="shared" si="34"/>
+        <f t="shared" si="33"/>
         <v>9.5238095238095219E-2</v>
       </c>
       <c r="K19" s="10">
-        <f t="shared" si="34"/>
+        <f t="shared" si="33"/>
         <v>-6.6176470588235299</v>
       </c>
       <c r="L19" s="10">
-        <f t="shared" si="34"/>
+        <f t="shared" si="33"/>
         <v>-0.39393939393939403</v>
       </c>
       <c r="M19" s="10">
-        <f t="shared" si="34"/>
+        <f t="shared" si="33"/>
         <v>-0.11764705882352945</v>
       </c>
       <c r="N19" s="10">
-        <f t="shared" si="34"/>
+        <f t="shared" si="33"/>
         <v>-0.19354838709677408</v>
       </c>
       <c r="O19" s="10">
-        <f t="shared" si="34"/>
+        <f t="shared" si="33"/>
         <v>-0.11764705882352938</v>
       </c>
       <c r="P19" s="10">
@@ -3460,95 +3457,95 @@
         <v>-0.14705882352941177</v>
       </c>
       <c r="Q19" s="10">
-        <f t="shared" ref="Q19:V19" si="35">Q7/Q3</f>
+        <f t="shared" ref="Q19:V19" si="34">Q7/Q3</f>
         <v>-0.26923076923076922</v>
       </c>
       <c r="R19" s="10">
-        <f t="shared" si="35"/>
+        <f t="shared" si="34"/>
         <v>-0.10344827586206898</v>
       </c>
       <c r="S19" s="10">
-        <f t="shared" si="35"/>
+        <f t="shared" si="34"/>
         <v>-0.18749999999999994</v>
       </c>
       <c r="T19" s="10">
-        <f t="shared" si="35"/>
+        <f t="shared" si="34"/>
         <v>-2.7777777777777801E-2</v>
       </c>
       <c r="U19" s="10">
-        <f t="shared" si="35"/>
-        <v>-0.1649450549450549</v>
+        <f t="shared" si="34"/>
+        <v>-0.17857142857142866</v>
       </c>
       <c r="V19" s="10">
-        <f t="shared" si="35"/>
-        <v>-9.2758620689655125E-2</v>
+        <f t="shared" si="34"/>
+        <v>-9.9028213166144227E-2</v>
       </c>
       <c r="X19" s="10">
-        <f t="shared" ref="X19" si="36">X7/X3</f>
+        <f t="shared" ref="X19" si="35">X7/X3</f>
         <v>-2.051282051282053E-2</v>
       </c>
       <c r="Y19" s="10">
-        <f t="shared" ref="Y19:AL19" si="37">Y7/Y3</f>
+        <f t="shared" ref="Y19:AL19" si="36">Y7/Y3</f>
         <v>5.1136363636363702E-2</v>
       </c>
       <c r="Z19" s="10">
-        <f t="shared" si="37"/>
+        <f t="shared" si="36"/>
         <v>-1.8931297709923665</v>
       </c>
       <c r="AA19" s="10">
-        <f t="shared" si="37"/>
+        <f t="shared" si="36"/>
         <v>-0.15447154471544702</v>
       </c>
       <c r="AB19" s="10">
-        <f t="shared" si="37"/>
-        <v>-0.11393638170974144</v>
+        <f t="shared" si="36"/>
+        <v>-0.11852228303362003</v>
       </c>
       <c r="AC19" s="10">
-        <f t="shared" si="37"/>
-        <v>-9.0391437781080358E-2</v>
+        <f t="shared" si="36"/>
+        <v>-8.1727617389764973E-2</v>
       </c>
       <c r="AD19" s="10">
-        <f t="shared" si="37"/>
-        <v>-7.6262277846342763E-2</v>
+        <f t="shared" si="36"/>
+        <v>-5.9048405015257044E-2</v>
       </c>
       <c r="AE19" s="10">
-        <f t="shared" si="37"/>
-        <v>-6.254868143909742E-2</v>
+        <f t="shared" si="36"/>
+        <v>-4.1609632004955807E-2</v>
       </c>
       <c r="AF19" s="10">
-        <f t="shared" si="37"/>
-        <v>-4.9238426102653318E-2</v>
+        <f t="shared" si="36"/>
+        <v>-2.8915231063633553E-2</v>
       </c>
       <c r="AG19" s="10">
-        <f t="shared" si="37"/>
-        <v>-3.6319648864340005E-2</v>
+        <f t="shared" si="36"/>
+        <v>-1.6594194855879658E-2</v>
       </c>
       <c r="AH19" s="10">
-        <f t="shared" si="37"/>
-        <v>-2.3780835662447625E-2</v>
+        <f t="shared" si="36"/>
+        <v>-4.6355420660007859E-3</v>
       </c>
       <c r="AI19" s="10">
-        <f t="shared" si="37"/>
-        <v>-1.161081108414023E-2</v>
+        <f t="shared" si="36"/>
+        <v>6.9713856418227461E-3</v>
       </c>
       <c r="AJ19" s="10">
-        <f t="shared" si="37"/>
-        <v>2.012715948050463E-4</v>
+        <f t="shared" si="36"/>
+        <v>1.8236933122945626E-2</v>
       </c>
       <c r="AK19" s="10">
-        <f t="shared" si="37"/>
-        <v>1.1665940077310762E-2</v>
+        <f t="shared" si="36"/>
+        <v>2.9171140972270797E-2</v>
       </c>
       <c r="AL19" s="10">
-        <f t="shared" si="37"/>
-        <v>2.2793412427978083E-2</v>
+        <f t="shared" si="36"/>
+        <v>3.978375447308638E-2</v>
       </c>
       <c r="AN19" t="s">
         <v>49</v>
       </c>
       <c r="AO19" s="2">
         <f>NPV(AO18,AB12:EI12)</f>
-        <v>3.877719450971314</v>
+        <v>4.8485508848212362</v>
       </c>
     </row>
     <row r="20" spans="2:41" x14ac:dyDescent="0.3">
@@ -3556,55 +3553,55 @@
         <v>27</v>
       </c>
       <c r="C20" s="10">
-        <f t="shared" ref="C20:O20" si="38">C11/C10</f>
+        <f t="shared" ref="C20:O20" si="37">C11/C10</f>
         <v>0</v>
       </c>
       <c r="D20" s="10">
-        <f t="shared" si="38"/>
+        <f t="shared" si="37"/>
         <v>0</v>
       </c>
       <c r="E20" s="10">
-        <f t="shared" si="38"/>
+        <f t="shared" si="37"/>
         <v>0</v>
       </c>
       <c r="F20" s="10">
-        <f t="shared" si="38"/>
+        <f t="shared" si="37"/>
         <v>0</v>
       </c>
       <c r="G20" s="10">
-        <f t="shared" si="38"/>
+        <f t="shared" si="37"/>
         <v>0</v>
       </c>
       <c r="H20" s="10">
-        <f t="shared" si="38"/>
+        <f t="shared" si="37"/>
         <v>0</v>
       </c>
       <c r="I20" s="10">
-        <f t="shared" si="38"/>
+        <f t="shared" si="37"/>
         <v>0</v>
       </c>
       <c r="J20" s="10">
-        <f t="shared" si="38"/>
+        <f t="shared" si="37"/>
         <v>0</v>
       </c>
       <c r="K20" s="10">
-        <f t="shared" si="38"/>
+        <f t="shared" si="37"/>
         <v>5.7142857142857141E-2</v>
       </c>
       <c r="L20" s="10">
-        <f t="shared" si="38"/>
+        <f t="shared" si="37"/>
         <v>8.3333333333333329E-2</v>
       </c>
       <c r="M20" s="10">
-        <f t="shared" si="38"/>
+        <f t="shared" si="37"/>
         <v>0</v>
       </c>
       <c r="N20" s="10">
-        <f t="shared" si="38"/>
+        <f t="shared" si="37"/>
         <v>0.25000000000000022</v>
       </c>
       <c r="O20" s="10">
-        <f t="shared" si="38"/>
+        <f t="shared" si="37"/>
         <v>0</v>
       </c>
       <c r="P20" s="10">
@@ -3612,87 +3609,87 @@
         <v>0</v>
       </c>
       <c r="Q20" s="10">
-        <f t="shared" ref="Q20:V20" si="39">Q11/Q10</f>
+        <f t="shared" ref="Q20:V20" si="38">Q11/Q10</f>
         <v>0.20000000000000004</v>
       </c>
       <c r="R20" s="10">
-        <f t="shared" si="39"/>
+        <f t="shared" si="38"/>
         <v>0</v>
       </c>
       <c r="S20" s="10">
-        <f t="shared" si="39"/>
+        <f t="shared" si="38"/>
         <v>0</v>
       </c>
       <c r="T20" s="10">
-        <f t="shared" si="39"/>
+        <f t="shared" si="38"/>
         <v>0</v>
       </c>
       <c r="U20" s="10">
-        <f t="shared" si="39"/>
+        <f t="shared" si="38"/>
         <v>0</v>
       </c>
       <c r="V20" s="10">
-        <f t="shared" si="39"/>
+        <f t="shared" si="38"/>
         <v>0</v>
       </c>
       <c r="X20" s="10">
-        <f t="shared" ref="X20" si="40">X11/X10</f>
+        <f t="shared" ref="X20" si="39">X11/X10</f>
         <v>0</v>
       </c>
       <c r="Y20" s="10">
-        <f t="shared" ref="Y20:AL20" si="41">Y11/Y10</f>
+        <f t="shared" ref="Y20:AL20" si="40">Y11/Y10</f>
         <v>0</v>
       </c>
       <c r="Z20" s="10">
-        <f t="shared" si="41"/>
+        <f t="shared" si="40"/>
         <v>3.4482758620689655E-2</v>
       </c>
       <c r="AA20" s="10">
-        <f t="shared" si="41"/>
+        <f t="shared" si="40"/>
         <v>9.0909090909091037E-2</v>
       </c>
       <c r="AB20" s="10">
-        <f t="shared" si="41"/>
+        <f t="shared" si="40"/>
         <v>0</v>
       </c>
       <c r="AC20" s="10">
-        <f t="shared" si="41"/>
+        <f t="shared" si="40"/>
         <v>0</v>
       </c>
       <c r="AD20" s="10">
-        <f t="shared" si="41"/>
+        <f t="shared" si="40"/>
         <v>0</v>
       </c>
       <c r="AE20" s="10">
-        <f t="shared" si="41"/>
+        <f t="shared" si="40"/>
         <v>0</v>
       </c>
       <c r="AF20" s="10">
-        <f t="shared" si="41"/>
+        <f t="shared" si="40"/>
         <v>0</v>
       </c>
       <c r="AG20" s="10">
-        <f t="shared" si="41"/>
+        <f t="shared" si="40"/>
         <v>0</v>
       </c>
       <c r="AH20" s="10">
-        <f t="shared" si="41"/>
+        <f t="shared" si="40"/>
         <v>0</v>
       </c>
       <c r="AI20" s="10">
-        <f t="shared" si="41"/>
+        <f t="shared" si="40"/>
         <v>0</v>
       </c>
       <c r="AJ20" s="10">
-        <f t="shared" si="41"/>
+        <f t="shared" si="40"/>
         <v>0</v>
       </c>
       <c r="AK20" s="10">
-        <f t="shared" si="41"/>
+        <f t="shared" si="40"/>
         <v>0</v>
       </c>
       <c r="AL20" s="10">
-        <f t="shared" si="41"/>
+        <f t="shared" si="40"/>
         <v>0</v>
       </c>
       <c r="AN20" t="s">
@@ -3700,7 +3697,7 @@
       </c>
       <c r="AO20" s="2">
         <f>Main!D8</f>
-        <v>19.7</v>
+        <v>20</v>
       </c>
     </row>
     <row r="21" spans="2:41" x14ac:dyDescent="0.3">
@@ -3708,55 +3705,55 @@
         <v>38</v>
       </c>
       <c r="C21" s="10">
-        <f t="shared" ref="C21:O21" si="42">C12/C3</f>
+        <f t="shared" ref="C21:O21" si="41">C12/C3</f>
         <v>3.84615384615382E-2</v>
       </c>
       <c r="D21" s="10">
-        <f t="shared" si="42"/>
+        <f t="shared" si="41"/>
         <v>0.1020408163265306</v>
       </c>
       <c r="E21" s="10">
-        <f t="shared" si="42"/>
+        <f t="shared" si="41"/>
         <v>-0.12499999999999997</v>
       </c>
       <c r="F21" s="10">
-        <f t="shared" si="42"/>
+        <f t="shared" si="41"/>
         <v>5.5555555555555643E-2</v>
       </c>
       <c r="G21" s="10">
-        <f t="shared" si="42"/>
+        <f t="shared" si="41"/>
         <v>-2.2727272727272613E-2</v>
       </c>
       <c r="H21" s="10">
-        <f t="shared" si="42"/>
+        <f t="shared" si="41"/>
         <v>0.13636363636363646</v>
       </c>
       <c r="I21" s="10">
-        <f t="shared" si="42"/>
+        <f t="shared" si="41"/>
         <v>6.5217391304347699E-2</v>
       </c>
       <c r="J21" s="10">
-        <f t="shared" si="42"/>
+        <f t="shared" si="41"/>
         <v>9.5238095238095219E-2</v>
       </c>
       <c r="K21" s="10">
-        <f t="shared" si="42"/>
+        <f t="shared" si="41"/>
         <v>2.9117647058823533</v>
       </c>
       <c r="L21" s="10">
-        <f t="shared" si="42"/>
+        <f t="shared" si="41"/>
         <v>-0.33333333333333337</v>
       </c>
       <c r="M21" s="10">
-        <f t="shared" si="42"/>
+        <f t="shared" si="41"/>
         <v>-5.8823529411764747E-2</v>
       </c>
       <c r="N21" s="10">
-        <f t="shared" si="42"/>
+        <f t="shared" si="41"/>
         <v>-9.6774193548386969E-2</v>
       </c>
       <c r="O21" s="10">
-        <f t="shared" si="42"/>
+        <f t="shared" si="41"/>
         <v>-5.8823529411764677E-2</v>
       </c>
       <c r="P21" s="10">
@@ -3764,95 +3761,95 @@
         <v>-8.8235294117647065E-2</v>
       </c>
       <c r="Q21" s="10">
-        <f t="shared" ref="Q21:V21" si="43">Q12/Q3</f>
+        <f t="shared" ref="Q21:V21" si="42">Q12/Q3</f>
         <v>-0.1538461538461538</v>
       </c>
       <c r="R21" s="10">
-        <f t="shared" si="43"/>
+        <f t="shared" si="42"/>
         <v>-3.4482758620689669E-2</v>
       </c>
       <c r="S21" s="10">
-        <f t="shared" si="43"/>
+        <f t="shared" si="42"/>
         <v>-0.12499999999999994</v>
       </c>
       <c r="T21" s="10">
-        <f t="shared" si="43"/>
+        <f t="shared" si="42"/>
         <v>2.7777777777777755E-2</v>
       </c>
       <c r="U21" s="10">
-        <f t="shared" si="43"/>
-        <v>-9.168498168498164E-2</v>
+        <f t="shared" si="42"/>
+        <v>-0.10714285714285722</v>
       </c>
       <c r="V21" s="10">
-        <f t="shared" si="43"/>
-        <v>-2.7077175697865306E-2</v>
+        <f t="shared" si="42"/>
+        <v>-3.6332288401253937E-2</v>
       </c>
       <c r="X21" s="10">
-        <f t="shared" ref="X21" si="44">X12/X3</f>
+        <f t="shared" ref="X21" si="43">X12/X3</f>
         <v>2.5641025641025623E-2</v>
       </c>
       <c r="Y21" s="10">
-        <f t="shared" ref="Y21:AL21" si="45">Y12/Y3</f>
+        <f t="shared" ref="Y21:AL21" si="44">Y12/Y3</f>
         <v>7.3863636363636423E-2</v>
       </c>
       <c r="Z21" s="10">
-        <f t="shared" si="45"/>
+        <f t="shared" si="44"/>
         <v>0.64122137404580148</v>
       </c>
       <c r="AA21" s="10">
-        <f t="shared" si="45"/>
+        <f t="shared" si="44"/>
         <v>-8.1300813008129955E-2</v>
       </c>
       <c r="AB21" s="10">
-        <f t="shared" si="45"/>
-        <v>-5.0318091451292131E-2</v>
+        <f t="shared" si="44"/>
+        <v>-5.5973416731821747E-2</v>
       </c>
       <c r="AC21" s="10">
-        <f t="shared" si="45"/>
-        <v>-2.7390800826111148E-2</v>
+        <f t="shared" si="44"/>
+        <v>-2.1539085665393049E-2</v>
       </c>
       <c r="AD21" s="10">
-        <f t="shared" si="45"/>
-        <v>-1.326164089137355E-2</v>
+        <f t="shared" si="44"/>
+        <v>-1.7345054815346883E-5</v>
       </c>
       <c r="AE21" s="10">
-        <f t="shared" si="45"/>
-        <v>4.5195551587179383E-4</v>
+        <f t="shared" si="44"/>
+        <v>1.6848310868491315E-2</v>
       </c>
       <c r="AF21" s="10">
-        <f t="shared" si="45"/>
-        <v>1.3762210852315901E-2</v>
+        <f t="shared" si="44"/>
+        <v>2.954271180981357E-2</v>
       </c>
       <c r="AG21" s="10">
-        <f t="shared" si="45"/>
-        <v>2.6680988090629215E-2</v>
+        <f t="shared" si="44"/>
+        <v>4.1863748017567468E-2</v>
       </c>
       <c r="AH21" s="10">
-        <f t="shared" si="45"/>
-        <v>3.9219801292521589E-2</v>
+        <f t="shared" si="44"/>
+        <v>5.3822400807446338E-2</v>
       </c>
       <c r="AI21" s="10">
-        <f t="shared" si="45"/>
-        <v>5.1389825870828978E-2</v>
+        <f t="shared" si="44"/>
+        <v>6.5429328515269863E-2</v>
       </c>
       <c r="AJ21" s="10">
-        <f t="shared" si="45"/>
-        <v>6.3201908549774255E-2</v>
+        <f t="shared" si="44"/>
+        <v>7.6694875996392742E-2</v>
       </c>
       <c r="AK21" s="10">
-        <f t="shared" si="45"/>
-        <v>7.4666577032279982E-2</v>
+        <f t="shared" si="44"/>
+        <v>8.7629083845717937E-2</v>
       </c>
       <c r="AL21" s="10">
-        <f t="shared" si="45"/>
-        <v>8.5794049382947296E-2</v>
+        <f t="shared" si="44"/>
+        <v>9.8241697346533499E-2</v>
       </c>
       <c r="AN21" t="s">
         <v>51</v>
       </c>
       <c r="AO21" s="2">
         <f>AO19+AO20</f>
-        <v>23.577719450971312</v>
+        <v>24.848550884821236</v>
       </c>
     </row>
     <row r="22" spans="2:41" x14ac:dyDescent="0.3">
@@ -3861,7 +3858,7 @@
       </c>
       <c r="AO22" s="9">
         <f>AO21/AL13</f>
-        <v>2.5082680266990756</v>
+        <v>2.6434628600873653</v>
       </c>
     </row>
     <row r="23" spans="2:41" x14ac:dyDescent="0.3">
@@ -3870,7 +3867,7 @@
       </c>
       <c r="AO23" s="9">
         <f>Main!D3</f>
-        <v>4.33</v>
+        <v>5.79</v>
       </c>
     </row>
     <row r="24" spans="2:41" x14ac:dyDescent="0.3">
@@ -3879,7 +3876,7 @@
       </c>
       <c r="AO24" s="11">
         <f>AO22/AO23-1</f>
-        <v>-0.42072331946903563</v>
+        <v>-0.54344337476902149</v>
       </c>
     </row>
     <row r="25" spans="2:41" x14ac:dyDescent="0.3">
